--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -26276,7 +26276,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 01, 2026 at 05:29 UTC</t>
+          <t>Last updated: May 01, 2026 at 05:34 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>5,016,052</t>
+          <t>5,189,019</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -569,22 +569,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>▲ 5.9% vs Apr 2025 (4,736,423 → 5,016,052)</t>
+          <t>▲ 9.6% vs Apr 2025 (4,736,423 → 5,189,019)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>▼ 7.2% vs Mar 2026 (5,403,169 → 5,016,052)</t>
+          <t>▼ 4.0% vs Mar 2026 (5,403,169 → 5,189,019)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>46.5% of Apr 2019 (10,779,665 baseline)</t>
+          <t>48.1% of Apr 2019 (10,779,665 baseline)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Large month-over-month swing (-7.2%) | Provisional — partial month, may be revised</t>
+          <t>Provisional — partial month, may be revised</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:45Z</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:25:59Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="L217" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="L221" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="L225" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L227" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="L229" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="L231" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="L237" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="L241" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="L243" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="L245" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11991,7 @@
       </c>
       <c r="L247" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="L249" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="L253" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="L255" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="L263" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="L265" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="L267" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="L269" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="L273" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="L275" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="L277" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13425,7 @@
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="L279" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="L281" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="L287" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="L289" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="L291" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="F293" s="4" t="n">
-        <v>5016052</v>
+        <v>5189019</v>
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L293" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:26:00Z</t>
+          <t>2026-05-01T06:00:46Z</t>
         </is>
       </c>
     </row>
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5016052</v>
+        <v>5189019</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5403169</v>
@@ -16956,17 +16956,17 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5016052</v>
+        <v>5189019</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4736423</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>279629</v>
+        <v>452596</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+9.6%</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -26276,7 +26276,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 01, 2026 at 05:34 UTC</t>
+          <t>Last updated: May 01, 2026 at 06:00 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:45Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="L217" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="L221" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="L225" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L227" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="L229" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="L231" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="L237" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="L241" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="L243" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="L245" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11991,7 @@
       </c>
       <c r="L247" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="L249" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="L253" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="L255" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="L263" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="L265" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="L267" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="L269" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="L273" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="L275" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="L277" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13425,7 @@
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="L279" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="L281" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="L287" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="L289" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="L291" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L293" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:00:46Z</t>
+          <t>2026-05-01T06:05:06Z</t>
         </is>
       </c>
     </row>
@@ -26276,7 +26276,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 01, 2026 at 06:00 UTC</t>
+          <t>Last updated: May 01, 2026 at 06:05 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>5,189,019</t>
+          <t>5,016,052</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -569,22 +569,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>▲ 9.6% vs Apr 2025 (4,736,423 → 5,189,019)</t>
+          <t>▲ 5.9% vs Apr 2025 (4,736,423 → 5,016,052)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>▼ 4.0% vs Mar 2026 (5,403,169 → 5,189,019)</t>
+          <t>▼ 7.2% vs Mar 2026 (5,403,169 → 5,016,052)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>48.1% of Apr 2019 (10,779,665 baseline)</t>
+          <t>46.5% of Apr 2019 (10,779,665 baseline)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Provisional — partial month, may be revised</t>
+          <t>Large month-over-month swing (-7.2%) | Provisional — partial month, may be revised</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6471,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9737,7 @@
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9829,7 @@
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10611,7 @@
       </c>
       <c r="L217" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="L221" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10887,7 @@
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="L225" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="L227" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="L229" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="L231" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11485,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
       </c>
       <c r="L237" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="L241" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="L243" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="L245" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11991,7 @@
       </c>
       <c r="L247" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="L249" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="L253" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="L255" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="L263" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="L265" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12865,7 @@
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12911,7 +12911,7 @@
       </c>
       <c r="L267" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12957,7 @@
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="L269" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13049,7 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="L273" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="L275" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13325,7 @@
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="L277" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13425,7 @@
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="L279" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="L281" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="L287" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14019,7 @@
       </c>
       <c r="L289" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="L291" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="F293" s="4" t="n">
-        <v>5189019</v>
+        <v>5016052</v>
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L293" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T06:05:06Z</t>
+          <t>2026-05-01T05:36:54Z</t>
         </is>
       </c>
     </row>
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5189019</v>
+        <v>5016052</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5403169</v>
@@ -16956,17 +16956,17 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5189019</v>
+        <v>5016052</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4736423</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>452596</v>
+        <v>279629</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>+9.6%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -26276,7 +26276,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 01, 2026 at 06:05 UTC</t>
+          <t>Last updated: May 02, 2026 at 09:14 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -26276,7 +26276,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 02, 2026 at 09:14 UTC</t>
+          <t>Last updated: May 02, 2026 at 19:58 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -56,7 +56,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -75,17 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,9 +111,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -498,10 +490,10 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
     <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -559,7 +551,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>5,016,052</t>
+          <t>5,233,814</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -569,22 +561,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>▲ 5.9% vs Apr 2025 (4,736,423 → 5,016,052)</t>
+          <t>▲ 10.5% vs Apr 2025 (4,736,423 → 5,233,814)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>▼ 7.2% vs Mar 2026 (5,403,169 → 5,016,052)</t>
+          <t>▼ 3.1% vs Mar 2026 (5,403,169 → 5,233,814)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>46.5% of Apr 2019 (10,779,665 baseline)</t>
+          <t>48.6% of Apr 2019 (10,779,665 baseline)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Large month-over-month swing (-7.2%) | Provisional — partial month, may be revised</t>
+          <t>Strong growth year-over-year (+10.5%)</t>
         </is>
       </c>
     </row>
@@ -721,7 +713,7 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -767,7 +759,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -813,7 +805,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -859,7 +851,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -905,7 +897,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -951,7 +943,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -997,7 +989,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1035,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1081,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1127,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1173,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1219,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1265,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1311,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1357,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1403,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1449,7 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1495,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1541,7 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1587,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1633,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1679,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1725,7 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1771,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1817,7 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1863,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1909,7 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1955,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2001,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2047,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2093,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2139,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2185,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2231,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2277,7 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2323,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2369,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2415,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2461,7 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2507,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2553,7 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2599,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2645,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2691,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2737,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2783,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2829,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2875,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2921,7 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2967,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3013,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3059,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3105,7 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3151,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3197,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3243,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3289,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3335,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3381,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3427,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3473,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3519,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3565,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3611,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3657,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3703,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3749,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3795,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3841,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3887,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3933,7 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3979,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4025,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4071,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4117,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4163,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4209,7 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4255,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4309,7 +4301,7 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4347,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4393,7 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4439,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4485,7 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4531,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4577,7 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4623,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4669,7 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4715,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4769,7 +4761,7 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4807,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4853,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4899,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4945,7 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4991,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5037,7 @@
       </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5083,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5129,7 @@
       </c>
       <c r="L98" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5175,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5221,7 @@
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5267,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5313,7 @@
       </c>
       <c r="L102" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5359,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5405,7 @@
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5451,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5497,7 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5543,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5589,7 @@
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5635,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5681,7 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5727,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5773,7 @@
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5819,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5865,7 @@
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5911,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5957,7 @@
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6003,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6049,7 @@
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6095,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6141,7 @@
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6187,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6233,7 @@
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6279,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6325,7 @@
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6371,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6417,7 @@
       </c>
       <c r="L126" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6471,7 +6463,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6509,7 @@
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6555,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6601,7 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6647,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6693,7 @@
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6739,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6785,7 @@
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6831,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6877,7 @@
       </c>
       <c r="L136" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6931,7 +6923,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6969,7 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7015,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7069,7 +7061,7 @@
       </c>
       <c r="L140" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7107,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7153,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7199,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7245,7 @@
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7291,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7345,7 +7337,7 @@
       </c>
       <c r="L146" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7383,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7429,7 @@
       </c>
       <c r="L148" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7475,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7521,7 @@
       </c>
       <c r="L150" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7567,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7613,7 @@
       </c>
       <c r="L152" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7659,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7705,7 @@
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7751,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7797,7 @@
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7843,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7889,7 @@
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7935,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7981,7 @@
       </c>
       <c r="L160" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8035,7 +8027,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8073,7 @@
       </c>
       <c r="L162" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8119,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8165,7 @@
       </c>
       <c r="L164" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8211,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8257,7 @@
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8303,7 @@
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8349,7 @@
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8395,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8441,7 @@
       </c>
       <c r="L170" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8487,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8533,7 @@
       </c>
       <c r="L172" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8587,7 +8579,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8625,7 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8671,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8717,7 @@
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8763,7 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8809,7 @@
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8855,7 @@
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8901,7 @@
       </c>
       <c r="L180" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8947,7 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9001,7 +8993,7 @@
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9039,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9085,7 @@
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9131,7 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9185,7 +9177,7 @@
       </c>
       <c r="L186" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9223,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9269,7 @@
       </c>
       <c r="L188" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9315,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9361,7 @@
       </c>
       <c r="L190" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9407,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9453,7 @@
       </c>
       <c r="L192" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9499,7 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9545,7 @@
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9591,7 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9645,7 +9637,7 @@
       </c>
       <c r="L196" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9683,7 @@
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9737,7 +9729,7 @@
       </c>
       <c r="L198" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9775,7 @@
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9821,7 @@
       </c>
       <c r="L200" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9867,7 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9921,7 +9913,7 @@
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -9967,7 +9959,7 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10005,7 @@
       </c>
       <c r="L204" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10059,7 +10051,7 @@
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10105,7 +10097,7 @@
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10143,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10189,7 @@
       </c>
       <c r="L208" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10235,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10289,7 +10281,7 @@
       </c>
       <c r="L210" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10327,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10373,7 @@
       </c>
       <c r="L212" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10419,7 @@
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10473,7 +10465,7 @@
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10511,7 @@
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10557,7 @@
       </c>
       <c r="L216" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10611,7 +10603,7 @@
       </c>
       <c r="L217" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10657,7 +10649,7 @@
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10695,7 @@
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10741,7 @@
       </c>
       <c r="L220" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10787,7 @@
       </c>
       <c r="L221" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10833,7 @@
       </c>
       <c r="L222" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10887,7 +10879,7 @@
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10925,7 @@
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10971,7 @@
       </c>
       <c r="L225" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11017,7 @@
       </c>
       <c r="L226" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11063,7 @@
       </c>
       <c r="L227" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11109,7 @@
       </c>
       <c r="L228" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11155,7 @@
       </c>
       <c r="L229" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11209,7 +11201,7 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11247,7 @@
       </c>
       <c r="L231" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11301,7 +11293,7 @@
       </c>
       <c r="L232" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11339,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11385,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11431,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11477,7 @@
       </c>
       <c r="L236" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11523,7 @@
       </c>
       <c r="L237" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11569,7 @@
       </c>
       <c r="L238" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11615,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11661,7 @@
       </c>
       <c r="L240" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11707,7 @@
       </c>
       <c r="L241" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11753,7 @@
       </c>
       <c r="L242" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11799,7 @@
       </c>
       <c r="L243" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11845,7 @@
       </c>
       <c r="L244" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11891,7 @@
       </c>
       <c r="L245" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11945,7 +11937,7 @@
       </c>
       <c r="L246" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11983,7 @@
       </c>
       <c r="L247" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12029,7 @@
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12075,7 @@
       </c>
       <c r="L249" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12129,7 +12121,7 @@
       </c>
       <c r="L250" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12167,7 @@
       </c>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12221,7 +12213,7 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12259,7 @@
       </c>
       <c r="L253" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12305,7 @@
       </c>
       <c r="L254" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12351,7 @@
       </c>
       <c r="L255" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12405,7 +12397,7 @@
       </c>
       <c r="L256" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12443,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12489,7 @@
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12535,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12581,7 @@
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12627,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12681,7 +12673,7 @@
       </c>
       <c r="L262" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12719,7 @@
       </c>
       <c r="L263" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12765,7 @@
       </c>
       <c r="L264" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12811,7 @@
       </c>
       <c r="L265" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12857,7 @@
       </c>
       <c r="L266" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12911,7 +12903,7 @@
       </c>
       <c r="L267" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -12957,7 +12949,7 @@
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13003,7 +12995,7 @@
       </c>
       <c r="L269" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13049,7 +13041,7 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13087,7 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13133,7 @@
       </c>
       <c r="L272" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13179,7 @@
       </c>
       <c r="L273" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13233,7 +13225,7 @@
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13271,7 @@
       </c>
       <c r="L275" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13325,7 +13317,7 @@
       </c>
       <c r="L276" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13363,7 @@
       </c>
       <c r="L277" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13417,7 @@
       </c>
       <c r="L278" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13479,7 +13471,7 @@
       </c>
       <c r="L279" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13533,7 +13525,7 @@
       </c>
       <c r="L280" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13579,7 @@
       </c>
       <c r="L281" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13641,7 +13633,7 @@
       </c>
       <c r="L282" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13687,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13749,7 +13741,7 @@
       </c>
       <c r="L284" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13795,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13849,7 @@
       </c>
       <c r="L286" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13903,7 @@
       </c>
       <c r="L287" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13957,7 @@
       </c>
       <c r="L288" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14011,7 @@
       </c>
       <c r="L289" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14065,7 @@
       </c>
       <c r="L290" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14119,7 @@
       </c>
       <c r="L291" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14163,7 @@
       </c>
       <c r="L292" s="3" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14192,7 @@
         </is>
       </c>
       <c r="F293" s="4" t="n">
-        <v>5016052</v>
+        <v>5233814</v>
       </c>
       <c r="G293" s="4" t="inlineStr">
         <is>
@@ -14211,11 +14203,11 @@
       <c r="I293" s="4" t="inlineStr"/>
       <c r="J293" s="4" t="n"/>
       <c r="K293" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L293" s="4" t="inlineStr">
         <is>
-          <t>2026-05-01T05:36:54Z</t>
+          <t>2026-05-02T20:29:59Z</t>
         </is>
       </c>
     </row>
@@ -16002,7 +15994,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5016052</v>
+        <v>5233814</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5403169</v>
@@ -16956,17 +16948,17 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5016052</v>
+        <v>5233814</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4736423</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>279629</v>
+        <v>497391</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+10.5%</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -17737,36 +17729,36 @@
       <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="2" t="n">
         <v>4767259</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="2" t="n">
         <v>4483736</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="2" t="n">
         <v>283523</v>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>+6.3%</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -17833,132 +17825,132 @@
       <c r="H27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>2024-02-01</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="2" t="n">
         <v>4211327</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="2" t="n">
         <v>3764194</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="2" t="n">
         <v>447133</v>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>+11.9%</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C29" s="2" t="n">
         <v>4133086</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="2" t="n">
         <v>3577697</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="2" t="n">
         <v>555389</v>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>+15.5%</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>2023-12-01</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="2" t="n">
         <v>3919728</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="2" t="n">
         <v>3569502</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="2" t="n">
         <v>350226</v>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>+9.8%</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>2023-11-01</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="2" t="n">
         <v>4311590</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="2" t="n">
         <v>3928429</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="2" t="n">
         <v>383161</v>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>+9.8%</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -18089,36 +18081,36 @@
       <c r="H35" s="4" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>2023-06-01</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C36" s="2" t="n">
         <v>4497899</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="2" t="n">
         <v>3999328</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="2" t="n">
         <v>498571</v>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>+12.5%</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="n"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -18377,132 +18369,132 @@
       <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="C45" s="2" t="n">
         <v>4399967</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="2" t="n">
         <v>2921077</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="2" t="n">
         <v>1478890</v>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>+50.6%</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>2022-08-01</t>
         </is>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="2" t="n">
         <v>4195650</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="2" t="n">
         <v>2643220</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="2" t="n">
         <v>1552430</v>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>+58.7%</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="n"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="C47" s="2" t="n">
         <v>3672785</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="2" t="n">
         <v>2391835</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="2" t="n">
         <v>1280950</v>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>+53.6%</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="n"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>2022-06-01</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="2" t="n">
         <v>3999328</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="2" t="n">
         <v>2127746</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="2" t="n">
         <v>1871582</v>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>+88.0%</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="n"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -18537,68 +18529,68 @@
       <c r="H49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C50" s="2" t="n">
         <v>3595725</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="2" t="n">
         <v>1597612</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="2" t="n">
         <v>1998113</v>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>+125.1%</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="n"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>2022-03-01</t>
         </is>
       </c>
-      <c r="C51" s="6" t="n">
+      <c r="C51" s="2" t="n">
         <v>3560435</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="2" t="n">
         <v>1482805</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="2" t="n">
         <v>2077630</v>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>+140.1%</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="n"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -18665,132 +18657,132 @@
       <c r="H53" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>2021-12-01</t>
         </is>
       </c>
-      <c r="C54" s="6" t="n">
+      <c r="C54" s="2" t="n">
         <v>2834892</v>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="2" t="n">
         <v>1216162</v>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E54" s="2" t="n">
         <v>1618730</v>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>+133.1%</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="n"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>2021-11-01</t>
         </is>
       </c>
-      <c r="C55" s="6" t="n">
+      <c r="C55" s="2" t="n">
         <v>2971042</v>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="2" t="n">
         <v>1331091</v>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="E55" s="2" t="n">
         <v>1639951</v>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>+123.2%</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="n"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="C56" s="6" t="n">
+      <c r="C56" s="2" t="n">
         <v>3057821</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="2" t="n">
         <v>1487371</v>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="E56" s="2" t="n">
         <v>1570450</v>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>+105.6%</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>2021-09-01</t>
         </is>
       </c>
-      <c r="C57" s="6" t="n">
+      <c r="C57" s="2" t="n">
         <v>2921077</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="2" t="n">
         <v>1291618</v>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" s="2" t="n">
         <v>1629459</v>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>+126.2%</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="n"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -18825,36 +18817,36 @@
       <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="C59" s="6" t="n">
+      <c r="C59" s="2" t="n">
         <v>2391835</v>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="2" t="n">
         <v>1270292</v>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E59" s="2" t="n">
         <v>1121543</v>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>+88.3%</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H59" s="6" t="n"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -18921,36 +18913,36 @@
       <c r="H61" s="4" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>2021-04-01</t>
         </is>
       </c>
-      <c r="C62" s="6" t="n">
+      <c r="C62" s="2" t="n">
         <v>1597612</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="2" t="n">
         <v>656653</v>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="E62" s="2" t="n">
         <v>940959</v>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>+143.3%</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="n"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -18985,100 +18977,100 @@
       <c r="H63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>2021-02-01</t>
         </is>
       </c>
-      <c r="C64" s="6" t="n">
+      <c r="C64" s="2" t="n">
         <v>1185642</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="2" t="n">
         <v>9527569</v>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E64" s="2" t="n">
         <v>-8341927</v>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>-87.6%</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>2021-01-01</t>
         </is>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C65" s="2" t="n">
         <v>1114032</v>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="2" t="n">
         <v>9925918</v>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="E65" s="2" t="n">
         <v>-8811886</v>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>-88.8%</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>2020-12-01</t>
         </is>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="2" t="n">
         <v>1216162</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="2" t="n">
         <v>9309469</v>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E66" s="2" t="n">
         <v>-8093307</v>
       </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>-86.9%</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="n"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -19113,68 +19105,68 @@
       <c r="H67" s="4" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>2020-10-01</t>
         </is>
       </c>
-      <c r="C68" s="6" t="n">
+      <c r="C68" s="2" t="n">
         <v>1487371</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="2" t="n">
         <v>11320625</v>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E68" s="2" t="n">
         <v>-9833254</v>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>-86.9%</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="n"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>2020-09-01</t>
         </is>
       </c>
-      <c r="C69" s="6" t="n">
+      <c r="C69" s="2" t="n">
         <v>1291618</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="2" t="n">
         <v>10505807</v>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E69" s="2" t="n">
         <v>-9214189</v>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>-87.7%</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="n"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -19209,100 +19201,100 @@
       <c r="H70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>2020-07-01</t>
         </is>
       </c>
-      <c r="C71" s="6" t="n">
+      <c r="C71" s="2" t="n">
         <v>1270292</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="2" t="n">
         <v>10625438</v>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E71" s="2" t="n">
         <v>-9355146</v>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>-88.0%</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H71" s="6" t="n"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>2020-06-01</t>
         </is>
       </c>
-      <c r="C72" s="6" t="n">
+      <c r="C72" s="2" t="n">
         <v>1095623</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="2" t="n">
         <v>10427019</v>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="E72" s="2" t="n">
         <v>-9331396</v>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>-89.5%</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="n"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>2020-05-01</t>
         </is>
       </c>
-      <c r="C73" s="6" t="n">
+      <c r="C73" s="2" t="n">
         <v>771234</v>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="2" t="n">
         <v>10801006</v>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="E73" s="2" t="n">
         <v>-10029772</v>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>-92.9%</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="n"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -19337,36 +19329,36 @@
       <c r="H74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>2020-03-01</t>
         </is>
       </c>
-      <c r="C75" s="6" t="n">
+      <c r="C75" s="2" t="n">
         <v>4308934</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="2" t="n">
         <v>10470980</v>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E75" s="2" t="n">
         <v>-6162046</v>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>-58.9%</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="n"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -19401,36 +19393,36 @@
       <c r="H76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>2020-01-01</t>
         </is>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C77" s="2" t="n">
         <v>9925918</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="2" t="n">
         <v>10106508</v>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E77" s="2" t="n">
         <v>-180590</v>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>-1.8%</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="n"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -19465,68 +19457,68 @@
       <c r="H78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="C79" s="6" t="n">
+      <c r="C79" s="2" t="n">
         <v>9728758</v>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="2" t="n">
         <v>9723261</v>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="E79" s="2" t="n">
         <v>5497</v>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>+0.1%</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="n"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>2019-10-01</t>
         </is>
       </c>
-      <c r="C80" s="6" t="n">
+      <c r="C80" s="2" t="n">
         <v>11320625</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="2" t="n">
         <v>11638526</v>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="E80" s="2" t="n">
         <v>-317901</v>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>-2.7%</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="n"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -19561,36 +19553,36 @@
       <c r="H81" s="4" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="C82" s="6" t="n">
+      <c r="C82" s="2" t="n">
         <v>10922850</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D82" s="2" t="n">
         <v>11227125</v>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="E82" s="2" t="n">
         <v>-304275</v>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>-2.7%</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H82" s="6" t="n"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -20457,36 +20449,36 @@
       <c r="H109" s="4" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="inlineStr">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>2017-04-01</t>
         </is>
       </c>
-      <c r="C110" s="6" t="n">
+      <c r="C110" s="2" t="n">
         <v>10411343</v>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="2" t="n">
         <v>11254160</v>
       </c>
-      <c r="E110" s="6" t="n">
+      <c r="E110" s="2" t="n">
         <v>-842817</v>
       </c>
-      <c r="F110" s="6" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>-7.5%</t>
         </is>
       </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H110" s="6" t="n"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -20585,68 +20577,68 @@
       <c r="H113" s="4" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>2016-12-01</t>
         </is>
       </c>
-      <c r="C114" s="6" t="n">
+      <c r="C114" s="2" t="n">
         <v>10519461</v>
       </c>
-      <c r="D114" s="6" t="n">
+      <c r="D114" s="2" t="n">
         <v>10915123</v>
       </c>
-      <c r="E114" s="6" t="n">
+      <c r="E114" s="2" t="n">
         <v>-395662</v>
       </c>
-      <c r="F114" s="6" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>-3.6%</t>
         </is>
       </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="n"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>2016-11-01</t>
         </is>
       </c>
-      <c r="C115" s="6" t="n">
+      <c r="C115" s="2" t="n">
         <v>10857637</v>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="2" t="n">
         <v>10720752</v>
       </c>
-      <c r="E115" s="6" t="n">
+      <c r="E115" s="2" t="n">
         <v>136885</v>
       </c>
-      <c r="F115" s="6" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>+1.3%</t>
         </is>
       </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H115" s="6" t="n"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -20681,100 +20673,100 @@
       <c r="H116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>2016-09-01</t>
         </is>
       </c>
-      <c r="C117" s="6" t="n">
+      <c r="C117" s="2" t="n">
         <v>11311307</v>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="2" t="n">
         <v>11449941</v>
       </c>
-      <c r="E117" s="6" t="n">
+      <c r="E117" s="2" t="n">
         <v>-138634</v>
       </c>
-      <c r="F117" s="6" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>-1.2%</t>
         </is>
       </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H117" s="6" t="n"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>2016-08-01</t>
         </is>
       </c>
-      <c r="C118" s="6" t="n">
+      <c r="C118" s="2" t="n">
         <v>11762450</v>
       </c>
-      <c r="D118" s="6" t="n">
+      <c r="D118" s="2" t="n">
         <v>11342101</v>
       </c>
-      <c r="E118" s="6" t="n">
+      <c r="E118" s="2" t="n">
         <v>420349</v>
       </c>
-      <c r="F118" s="6" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>+3.7%</t>
         </is>
       </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H118" s="6" t="n"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="C119" s="6" t="n">
+      <c r="C119" s="2" t="n">
         <v>10944760</v>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="2" t="n">
         <v>11731661</v>
       </c>
-      <c r="E119" s="6" t="n">
+      <c r="E119" s="2" t="n">
         <v>-786901</v>
       </c>
-      <c r="F119" s="6" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>-6.7%</t>
         </is>
       </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H119" s="6" t="n"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -20809,196 +20801,196 @@
       <c r="H120" s="3" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>2016-05-01</t>
         </is>
       </c>
-      <c r="C121" s="6" t="n">
+      <c r="C121" s="2" t="n">
         <v>11432356</v>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="2" t="n">
         <v>11041447</v>
       </c>
-      <c r="E121" s="6" t="n">
+      <c r="E121" s="2" t="n">
         <v>390909</v>
       </c>
-      <c r="F121" s="6" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>+3.5%</t>
         </is>
       </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H121" s="6" t="n"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>2016-04-01</t>
         </is>
       </c>
-      <c r="C122" s="6" t="n">
+      <c r="C122" s="2" t="n">
         <v>11254160</v>
       </c>
-      <c r="D122" s="6" t="n">
+      <c r="D122" s="2" t="n">
         <v>11468925</v>
       </c>
-      <c r="E122" s="6" t="n">
+      <c r="E122" s="2" t="n">
         <v>-214765</v>
       </c>
-      <c r="F122" s="6" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>-1.9%</t>
         </is>
       </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H122" s="6" t="n"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>2016-03-01</t>
         </is>
       </c>
-      <c r="C123" s="6" t="n">
+      <c r="C123" s="2" t="n">
         <v>11744295</v>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D123" s="2" t="n">
         <v>11563999</v>
       </c>
-      <c r="E123" s="6" t="n">
+      <c r="E123" s="2" t="n">
         <v>180296</v>
       </c>
-      <c r="F123" s="6" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>+1.6%</t>
         </is>
       </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H123" s="6" t="n"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>2016-02-01</t>
         </is>
       </c>
-      <c r="C124" s="6" t="n">
+      <c r="C124" s="2" t="n">
         <v>11457041</v>
       </c>
-      <c r="D124" s="6" t="n">
+      <c r="D124" s="2" t="n">
         <v>10136239</v>
       </c>
-      <c r="E124" s="6" t="n">
+      <c r="E124" s="2" t="n">
         <v>1320802</v>
       </c>
-      <c r="F124" s="6" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>+13.0%</t>
         </is>
       </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="n"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="C125" s="6" t="n">
+      <c r="C125" s="2" t="n">
         <v>10648753</v>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D125" s="2" t="n">
         <v>10565314</v>
       </c>
-      <c r="E125" s="6" t="n">
+      <c r="E125" s="2" t="n">
         <v>83439</v>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>+0.8%</t>
         </is>
       </c>
-      <c r="G125" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H125" s="6" t="n"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>2015-12-01</t>
         </is>
       </c>
-      <c r="C126" s="6" t="n">
+      <c r="C126" s="2" t="n">
         <v>10915123</v>
       </c>
-      <c r="D126" s="6" t="n">
+      <c r="D126" s="2" t="n">
         <v>10688033</v>
       </c>
-      <c r="E126" s="6" t="n">
+      <c r="E126" s="2" t="n">
         <v>227090</v>
       </c>
-      <c r="F126" s="6" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>+2.1%</t>
         </is>
       </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H126" s="6" t="n"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -21033,68 +21025,68 @@
       <c r="H127" s="4" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>2015-10-01</t>
         </is>
       </c>
-      <c r="C128" s="6" t="n">
+      <c r="C128" s="2" t="n">
         <v>12202108</v>
       </c>
-      <c r="D128" s="6" t="n">
+      <c r="D128" s="2" t="n">
         <v>12556439</v>
       </c>
-      <c r="E128" s="6" t="n">
+      <c r="E128" s="2" t="n">
         <v>-354331</v>
       </c>
-      <c r="F128" s="6" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>-2.8%</t>
         </is>
       </c>
-      <c r="G128" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H128" s="6" t="n"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>2015-09-01</t>
         </is>
       </c>
-      <c r="C129" s="6" t="n">
+      <c r="C129" s="2" t="n">
         <v>11449941</v>
       </c>
-      <c r="D129" s="6" t="n">
+      <c r="D129" s="2" t="n">
         <v>11467457</v>
       </c>
-      <c r="E129" s="6" t="n">
+      <c r="E129" s="2" t="n">
         <v>-17516</v>
       </c>
-      <c r="F129" s="6" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="G129" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H129" s="6" t="n"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -21129,68 +21121,68 @@
       <c r="H130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>2015-07-01</t>
         </is>
       </c>
-      <c r="C131" s="6" t="n">
+      <c r="C131" s="2" t="n">
         <v>11731661</v>
       </c>
-      <c r="D131" s="6" t="n">
+      <c r="D131" s="2" t="n">
         <v>11529147</v>
       </c>
-      <c r="E131" s="6" t="n">
+      <c r="E131" s="2" t="n">
         <v>202514</v>
       </c>
-      <c r="F131" s="6" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>+1.8%</t>
         </is>
       </c>
-      <c r="G131" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H131" s="6" t="n"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>2015-06-01</t>
         </is>
       </c>
-      <c r="C132" s="6" t="n">
+      <c r="C132" s="2" t="n">
         <v>11849485</v>
       </c>
-      <c r="D132" s="6" t="n">
+      <c r="D132" s="2" t="n">
         <v>11145026</v>
       </c>
-      <c r="E132" s="6" t="n">
+      <c r="E132" s="2" t="n">
         <v>704459</v>
       </c>
-      <c r="F132" s="6" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>+6.3%</t>
         </is>
       </c>
-      <c r="G132" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="n"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -21289,100 +21281,100 @@
       <c r="H135" s="4" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>2015-02-01</t>
         </is>
       </c>
-      <c r="C136" s="6" t="n">
+      <c r="C136" s="2" t="n">
         <v>10136239</v>
       </c>
-      <c r="D136" s="6" t="n">
+      <c r="D136" s="2" t="n">
         <v>9708516</v>
       </c>
-      <c r="E136" s="6" t="n">
+      <c r="E136" s="2" t="n">
         <v>427723</v>
       </c>
-      <c r="F136" s="6" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>+4.4%</t>
         </is>
       </c>
-      <c r="G136" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H136" s="6" t="n"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="C137" s="6" t="n">
+      <c r="C137" s="2" t="n">
         <v>10565314</v>
       </c>
-      <c r="D137" s="6" t="n">
+      <c r="D137" s="2" t="n">
         <v>10275255</v>
       </c>
-      <c r="E137" s="6" t="n">
+      <c r="E137" s="2" t="n">
         <v>290059</v>
       </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>+2.8%</t>
         </is>
       </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H137" s="6" t="n"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B138" s="6" t="inlineStr">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>2014-12-01</t>
         </is>
       </c>
-      <c r="C138" s="6" t="n">
+      <c r="C138" s="2" t="n">
         <v>10688033</v>
       </c>
-      <c r="D138" s="6" t="n">
+      <c r="D138" s="2" t="n">
         <v>10196072</v>
       </c>
-      <c r="E138" s="6" t="n">
+      <c r="E138" s="2" t="n">
         <v>491961</v>
       </c>
-      <c r="F138" s="6" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>+4.8%</t>
         </is>
       </c>
-      <c r="G138" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H138" s="6" t="n"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -21481,36 +21473,36 @@
       <c r="H141" s="4" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B142" s="6" t="inlineStr">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>2014-08-01</t>
         </is>
       </c>
-      <c r="C142" s="6" t="n">
+      <c r="C142" s="2" t="n">
         <v>11455046</v>
       </c>
-      <c r="D142" s="6" t="n">
+      <c r="D142" s="2" t="n">
         <v>11271687</v>
       </c>
-      <c r="E142" s="6" t="n">
+      <c r="E142" s="2" t="n">
         <v>183359</v>
       </c>
-      <c r="F142" s="6" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>+1.6%</t>
         </is>
       </c>
-      <c r="G142" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="n"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -21577,36 +21569,36 @@
       <c r="H144" s="3" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>2014-05-01</t>
         </is>
       </c>
-      <c r="C145" s="6" t="n">
+      <c r="C145" s="2" t="n">
         <v>11184320</v>
       </c>
-      <c r="D145" s="6" t="n">
+      <c r="D145" s="2" t="n">
         <v>11107331</v>
       </c>
-      <c r="E145" s="6" t="n">
+      <c r="E145" s="2" t="n">
         <v>76989</v>
       </c>
-      <c r="F145" s="6" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>+0.7%</t>
         </is>
       </c>
-      <c r="G145" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H145" s="6" t="n"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -21769,68 +21761,68 @@
       <c r="H150" s="3" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="C151" s="6" t="n">
+      <c r="C151" s="2" t="n">
         <v>10100407</v>
       </c>
-      <c r="D151" s="6" t="n">
+      <c r="D151" s="2" t="n">
         <v>10225693</v>
       </c>
-      <c r="E151" s="6" t="n">
+      <c r="E151" s="2" t="n">
         <v>-125286</v>
       </c>
-      <c r="F151" s="6" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>-1.2%</t>
         </is>
       </c>
-      <c r="G151" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H151" s="6" t="n"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>2013-10-01</t>
         </is>
       </c>
-      <c r="C152" s="6" t="n">
+      <c r="C152" s="2" t="n">
         <v>10007386</v>
       </c>
-      <c r="D152" s="6" t="n">
+      <c r="D152" s="2" t="n">
         <v>11975954</v>
       </c>
-      <c r="E152" s="6" t="n">
+      <c r="E152" s="2" t="n">
         <v>-1968568</v>
       </c>
-      <c r="F152" s="6" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>-16.4%</t>
         </is>
       </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H152" s="6" t="n"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -21897,36 +21889,36 @@
       <c r="H154" s="3" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B155" s="6" t="inlineStr">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>2013-07-01</t>
         </is>
       </c>
-      <c r="C155" s="6" t="n">
+      <c r="C155" s="2" t="n">
         <v>9005234</v>
       </c>
-      <c r="D155" s="6" t="n">
+      <c r="D155" s="2" t="n">
         <v>10252748</v>
       </c>
-      <c r="E155" s="6" t="n">
+      <c r="E155" s="2" t="n">
         <v>-1247514</v>
       </c>
-      <c r="F155" s="6" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>-12.2%</t>
         </is>
       </c>
-      <c r="G155" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H155" s="6" t="n"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -22057,36 +22049,36 @@
       <c r="H159" s="4" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B160" s="6" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>2013-02-01</t>
         </is>
       </c>
-      <c r="C160" s="6" t="n">
+      <c r="C160" s="2" t="n">
         <v>9720752</v>
       </c>
-      <c r="D160" s="6" t="n">
+      <c r="D160" s="2" t="n">
         <v>9663403</v>
       </c>
-      <c r="E160" s="6" t="n">
+      <c r="E160" s="2" t="n">
         <v>57349</v>
       </c>
-      <c r="F160" s="6" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>+0.6%</t>
         </is>
       </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H160" s="6" t="n"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -22153,36 +22145,36 @@
       <c r="H162" s="3" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>2012-11-01</t>
         </is>
       </c>
-      <c r="C163" s="6" t="n">
+      <c r="C163" s="2" t="n">
         <v>10225693</v>
       </c>
-      <c r="D163" s="6" t="n">
+      <c r="D163" s="2" t="n">
         <v>9511142</v>
       </c>
-      <c r="E163" s="6" t="n">
+      <c r="E163" s="2" t="n">
         <v>714551</v>
       </c>
-      <c r="F163" s="6" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>+7.5%</t>
         </is>
       </c>
-      <c r="G163" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H163" s="6" t="n"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -22409,36 +22401,36 @@
       <c r="H170" s="3" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B171" s="6" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>2012-03-01</t>
         </is>
       </c>
-      <c r="C171" s="6" t="n">
+      <c r="C171" s="2" t="n">
         <v>10063110</v>
       </c>
-      <c r="D171" s="6" t="n">
+      <c r="D171" s="2" t="n">
         <v>9555408</v>
       </c>
-      <c r="E171" s="6" t="n">
+      <c r="E171" s="2" t="n">
         <v>507702</v>
       </c>
-      <c r="F171" s="6" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>+5.3%</t>
         </is>
       </c>
-      <c r="G171" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H171" s="6" t="n"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -24393,932 +24385,932 @@
       <c r="H232" s="5" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B233" s="6" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>2007-01-01</t>
         </is>
       </c>
-      <c r="C233" s="6" t="n">
+      <c r="C233" s="2" t="n">
         <v>8670049</v>
       </c>
-      <c r="D233" s="6" t="n">
+      <c r="D233" s="2" t="n">
         <v>8153875</v>
       </c>
-      <c r="E233" s="6" t="n">
+      <c r="E233" s="2" t="n">
         <v>516174</v>
       </c>
-      <c r="F233" s="6" t="inlineStr">
+      <c r="F233" s="2" t="inlineStr">
         <is>
           <t>+6.3%</t>
         </is>
       </c>
-      <c r="G233" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H233" s="6" t="n"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B234" s="6" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>2006-12-01</t>
         </is>
       </c>
-      <c r="C234" s="6" t="n">
+      <c r="C234" s="2" t="n">
         <v>8589717</v>
       </c>
-      <c r="D234" s="6" t="n">
+      <c r="D234" s="2" t="n">
         <v>8222205</v>
       </c>
-      <c r="E234" s="6" t="n">
+      <c r="E234" s="2" t="n">
         <v>367512</v>
       </c>
-      <c r="F234" s="6" t="inlineStr">
+      <c r="F234" s="2" t="inlineStr">
         <is>
           <t>+4.5%</t>
         </is>
       </c>
-      <c r="G234" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H234" s="6" t="n"/>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B235" s="6" t="inlineStr">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>2006-11-01</t>
         </is>
       </c>
-      <c r="C235" s="6" t="n">
+      <c r="C235" s="2" t="n">
         <v>8886575</v>
       </c>
-      <c r="D235" s="6" t="n">
+      <c r="D235" s="2" t="n">
         <v>8696359</v>
       </c>
-      <c r="E235" s="6" t="n">
+      <c r="E235" s="2" t="n">
         <v>190216</v>
       </c>
-      <c r="F235" s="6" t="inlineStr">
+      <c r="F235" s="2" t="inlineStr">
         <is>
           <t>+2.2%</t>
         </is>
       </c>
-      <c r="G235" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H235" s="6" t="n"/>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B236" s="6" t="inlineStr">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>2006-10-01</t>
         </is>
       </c>
-      <c r="C236" s="6" t="n">
+      <c r="C236" s="2" t="n">
         <v>9657712</v>
       </c>
-      <c r="D236" s="6" t="n">
+      <c r="D236" s="2" t="n">
         <v>9150357</v>
       </c>
-      <c r="E236" s="6" t="n">
+      <c r="E236" s="2" t="n">
         <v>507355</v>
       </c>
-      <c r="F236" s="6" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>+5.5%</t>
         </is>
       </c>
-      <c r="G236" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H236" s="6" t="n"/>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B237" s="6" t="inlineStr">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>2006-09-01</t>
         </is>
       </c>
-      <c r="C237" s="6" t="n">
+      <c r="C237" s="2" t="n">
         <v>9164925</v>
       </c>
-      <c r="D237" s="6" t="n">
+      <c r="D237" s="2" t="n">
         <v>9055094</v>
       </c>
-      <c r="E237" s="6" t="n">
+      <c r="E237" s="2" t="n">
         <v>109831</v>
       </c>
-      <c r="F237" s="6" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>+1.2%</t>
         </is>
       </c>
-      <c r="G237" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H237" s="6" t="n"/>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B238" s="6" t="inlineStr">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>2006-08-01</t>
         </is>
       </c>
-      <c r="C238" s="6" t="n">
+      <c r="C238" s="2" t="n">
         <v>9408203</v>
       </c>
-      <c r="D238" s="6" t="n">
+      <c r="D238" s="2" t="n">
         <v>8931804</v>
       </c>
-      <c r="E238" s="6" t="n">
+      <c r="E238" s="2" t="n">
         <v>476399</v>
       </c>
-      <c r="F238" s="6" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>+5.3%</t>
         </is>
       </c>
-      <c r="G238" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H238" s="6" t="n"/>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B239" s="6" t="inlineStr">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>2006-07-01</t>
         </is>
       </c>
-      <c r="C239" s="6" t="n">
+      <c r="C239" s="2" t="n">
         <v>8841429</v>
       </c>
-      <c r="D239" s="6" t="n">
+      <c r="D239" s="2" t="n">
         <v>8166483</v>
       </c>
-      <c r="E239" s="6" t="n">
+      <c r="E239" s="2" t="n">
         <v>674946</v>
       </c>
-      <c r="F239" s="6" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>+8.3%</t>
         </is>
       </c>
-      <c r="G239" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H239" s="6" t="n"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B240" s="6" t="inlineStr">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>2006-06-01</t>
         </is>
       </c>
-      <c r="C240" s="6" t="n">
+      <c r="C240" s="2" t="n">
         <v>9129312</v>
       </c>
-      <c r="D240" s="6" t="n">
+      <c r="D240" s="2" t="n">
         <v>8556260</v>
       </c>
-      <c r="E240" s="6" t="n">
+      <c r="E240" s="2" t="n">
         <v>573052</v>
       </c>
-      <c r="F240" s="6" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>+6.7%</t>
         </is>
       </c>
-      <c r="G240" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H240" s="6" t="n"/>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B241" s="6" t="inlineStr">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>2006-05-01</t>
         </is>
       </c>
-      <c r="C241" s="6" t="n">
+      <c r="C241" s="2" t="n">
         <v>9199520</v>
       </c>
-      <c r="D241" s="6" t="n">
+      <c r="D241" s="2" t="n">
         <v>8565848</v>
       </c>
-      <c r="E241" s="6" t="n">
+      <c r="E241" s="2" t="n">
         <v>633672</v>
       </c>
-      <c r="F241" s="6" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>+7.4%</t>
         </is>
       </c>
-      <c r="G241" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H241" s="6" t="n"/>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B242" s="6" t="inlineStr">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>2006-04-01</t>
         </is>
       </c>
-      <c r="C242" s="6" t="n">
+      <c r="C242" s="2" t="n">
         <v>8254952</v>
       </c>
-      <c r="D242" s="6" t="n">
+      <c r="D242" s="2" t="n">
         <v>8368549</v>
       </c>
-      <c r="E242" s="6" t="n">
+      <c r="E242" s="2" t="n">
         <v>-113597</v>
       </c>
-      <c r="F242" s="6" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>-1.4%</t>
         </is>
       </c>
-      <c r="G242" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H242" s="6" t="n"/>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B243" s="6" t="inlineStr">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
         <is>
           <t>2006-03-01</t>
         </is>
       </c>
-      <c r="C243" s="6" t="n">
+      <c r="C243" s="2" t="n">
         <v>8826982</v>
       </c>
-      <c r="D243" s="6" t="n">
+      <c r="D243" s="2" t="n">
         <v>8607197</v>
       </c>
-      <c r="E243" s="6" t="n">
+      <c r="E243" s="2" t="n">
         <v>219785</v>
       </c>
-      <c r="F243" s="6" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>+2.5%</t>
         </is>
       </c>
-      <c r="G243" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H243" s="6" t="n"/>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B244" s="6" t="inlineStr">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>2006-02-01</t>
         </is>
       </c>
-      <c r="C244" s="6" t="n">
+      <c r="C244" s="2" t="n">
         <v>7867174</v>
       </c>
-      <c r="D244" s="6" t="n">
+      <c r="D244" s="2" t="n">
         <v>7468182</v>
       </c>
-      <c r="E244" s="6" t="n">
+      <c r="E244" s="2" t="n">
         <v>398992</v>
       </c>
-      <c r="F244" s="6" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>+5.3%</t>
         </is>
       </c>
-      <c r="G244" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H244" s="6" t="n"/>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B245" s="6" t="inlineStr">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>2006-01-01</t>
         </is>
       </c>
-      <c r="C245" s="6" t="n">
+      <c r="C245" s="2" t="n">
         <v>8153875</v>
       </c>
-      <c r="D245" s="6" t="n">
+      <c r="D245" s="2" t="n">
         <v>7702994</v>
       </c>
-      <c r="E245" s="6" t="n">
+      <c r="E245" s="2" t="n">
         <v>450881</v>
       </c>
-      <c r="F245" s="6" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>+5.9%</t>
         </is>
       </c>
-      <c r="G245" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H245" s="6" t="n"/>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B246" s="6" t="inlineStr">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>2005-12-01</t>
         </is>
       </c>
-      <c r="C246" s="6" t="n">
+      <c r="C246" s="2" t="n">
         <v>8222205</v>
       </c>
-      <c r="D246" s="6" t="n">
+      <c r="D246" s="2" t="n">
         <v>8099384</v>
       </c>
-      <c r="E246" s="6" t="n">
+      <c r="E246" s="2" t="n">
         <v>122821</v>
       </c>
-      <c r="F246" s="6" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>+1.5%</t>
         </is>
       </c>
-      <c r="G246" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H246" s="6" t="n"/>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B247" s="6" t="inlineStr">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>2005-11-01</t>
         </is>
       </c>
-      <c r="C247" s="6" t="n">
+      <c r="C247" s="2" t="n">
         <v>8696359</v>
       </c>
-      <c r="D247" s="6" t="n">
+      <c r="D247" s="2" t="n">
         <v>8152569</v>
       </c>
-      <c r="E247" s="6" t="n">
+      <c r="E247" s="2" t="n">
         <v>543790</v>
       </c>
-      <c r="F247" s="6" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>+6.7%</t>
         </is>
       </c>
-      <c r="G247" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H247" s="6" t="n"/>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B248" s="6" t="inlineStr">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>2005-10-01</t>
         </is>
       </c>
-      <c r="C248" s="6" t="n">
+      <c r="C248" s="2" t="n">
         <v>9150357</v>
       </c>
-      <c r="D248" s="6" t="n">
+      <c r="D248" s="2" t="n">
         <v>8524930</v>
       </c>
-      <c r="E248" s="6" t="n">
+      <c r="E248" s="2" t="n">
         <v>625427</v>
       </c>
-      <c r="F248" s="6" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>+7.3%</t>
         </is>
       </c>
-      <c r="G248" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H248" s="6" t="n"/>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B249" s="6" t="inlineStr">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>2005-09-01</t>
         </is>
       </c>
-      <c r="C249" s="6" t="n">
+      <c r="C249" s="2" t="n">
         <v>9055094</v>
       </c>
-      <c r="D249" s="6" t="n">
+      <c r="D249" s="2" t="n">
         <v>8599271</v>
       </c>
-      <c r="E249" s="6" t="n">
+      <c r="E249" s="2" t="n">
         <v>455823</v>
       </c>
-      <c r="F249" s="6" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>+5.3%</t>
         </is>
       </c>
-      <c r="G249" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H249" s="6" t="n"/>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B250" s="6" t="inlineStr">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>2005-08-01</t>
         </is>
       </c>
-      <c r="C250" s="6" t="n">
+      <c r="C250" s="2" t="n">
         <v>8931804</v>
       </c>
-      <c r="D250" s="6" t="n">
+      <c r="D250" s="2" t="n">
         <v>8360745</v>
       </c>
-      <c r="E250" s="6" t="n">
+      <c r="E250" s="2" t="n">
         <v>571059</v>
       </c>
-      <c r="F250" s="6" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>+6.8%</t>
         </is>
       </c>
-      <c r="G250" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H250" s="6" t="n"/>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B251" s="6" t="inlineStr">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>2005-07-01</t>
         </is>
       </c>
-      <c r="C251" s="6" t="n">
+      <c r="C251" s="2" t="n">
         <v>8166483</v>
       </c>
-      <c r="D251" s="6" t="n">
+      <c r="D251" s="2" t="n">
         <v>8290098</v>
       </c>
-      <c r="E251" s="6" t="n">
+      <c r="E251" s="2" t="n">
         <v>-123615</v>
       </c>
-      <c r="F251" s="6" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>-1.5%</t>
         </is>
       </c>
-      <c r="G251" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H251" s="6" t="n"/>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B252" s="6" t="inlineStr">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>2005-06-01</t>
         </is>
       </c>
-      <c r="C252" s="6" t="n">
+      <c r="C252" s="2" t="n">
         <v>8556260</v>
       </c>
-      <c r="D252" s="6" t="n">
+      <c r="D252" s="2" t="n">
         <v>8416224</v>
       </c>
-      <c r="E252" s="6" t="n">
+      <c r="E252" s="2" t="n">
         <v>140036</v>
       </c>
-      <c r="F252" s="6" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>+1.7%</t>
         </is>
       </c>
-      <c r="G252" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H252" s="6" t="n"/>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B253" s="6" t="inlineStr">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>2005-05-01</t>
         </is>
       </c>
-      <c r="C253" s="6" t="n">
+      <c r="C253" s="2" t="n">
         <v>8565848</v>
       </c>
-      <c r="D253" s="6" t="n">
+      <c r="D253" s="2" t="n">
         <v>8224919</v>
       </c>
-      <c r="E253" s="6" t="n">
+      <c r="E253" s="2" t="n">
         <v>340929</v>
       </c>
-      <c r="F253" s="6" t="inlineStr">
+      <c r="F253" s="2" t="inlineStr">
         <is>
           <t>+4.2%</t>
         </is>
       </c>
-      <c r="G253" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H253" s="6" t="n"/>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B254" s="6" t="inlineStr">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>2005-04-01</t>
         </is>
       </c>
-      <c r="C254" s="6" t="n">
+      <c r="C254" s="2" t="n">
         <v>8368549</v>
       </c>
-      <c r="D254" s="6" t="n">
+      <c r="D254" s="2" t="n">
         <v>8332090</v>
       </c>
-      <c r="E254" s="6" t="n">
+      <c r="E254" s="2" t="n">
         <v>36459</v>
       </c>
-      <c r="F254" s="6" t="inlineStr">
+      <c r="F254" s="2" t="inlineStr">
         <is>
           <t>+0.4%</t>
         </is>
       </c>
-      <c r="G254" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H254" s="6" t="n"/>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B255" s="6" t="inlineStr">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>2005-03-01</t>
         </is>
       </c>
-      <c r="C255" s="6" t="n">
+      <c r="C255" s="2" t="n">
         <v>8607197</v>
       </c>
-      <c r="D255" s="6" t="n">
+      <c r="D255" s="2" t="n">
         <v>8574110</v>
       </c>
-      <c r="E255" s="6" t="n">
+      <c r="E255" s="2" t="n">
         <v>33087</v>
       </c>
-      <c r="F255" s="6" t="inlineStr">
+      <c r="F255" s="2" t="inlineStr">
         <is>
           <t>+0.4%</t>
         </is>
       </c>
-      <c r="G255" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H255" s="6" t="n"/>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B256" s="6" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>2005-02-01</t>
         </is>
       </c>
-      <c r="C256" s="6" t="n">
+      <c r="C256" s="2" t="n">
         <v>7468182</v>
       </c>
-      <c r="D256" s="6" t="n">
+      <c r="D256" s="2" t="n">
         <v>7475394</v>
       </c>
-      <c r="E256" s="6" t="n">
+      <c r="E256" s="2" t="n">
         <v>-7212</v>
       </c>
-      <c r="F256" s="6" t="inlineStr">
+      <c r="F256" s="2" t="inlineStr">
         <is>
           <t>-0.1%</t>
         </is>
       </c>
-      <c r="G256" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H256" s="6" t="n"/>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B257" s="6" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>2005-01-01</t>
         </is>
       </c>
-      <c r="C257" s="6" t="n">
+      <c r="C257" s="2" t="n">
         <v>7702994</v>
       </c>
-      <c r="D257" s="6" t="n">
+      <c r="D257" s="2" t="n">
         <v>7580822</v>
       </c>
-      <c r="E257" s="6" t="n">
+      <c r="E257" s="2" t="n">
         <v>122172</v>
       </c>
-      <c r="F257" s="6" t="inlineStr">
+      <c r="F257" s="2" t="inlineStr">
         <is>
           <t>+1.6%</t>
         </is>
       </c>
-      <c r="G257" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H257" s="6" t="n"/>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B258" s="6" t="inlineStr">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>2004-12-01</t>
         </is>
       </c>
-      <c r="C258" s="6" t="n">
+      <c r="C258" s="2" t="n">
         <v>8099384</v>
       </c>
-      <c r="D258" s="6" t="n">
+      <c r="D258" s="2" t="n">
         <v>7916215</v>
       </c>
-      <c r="E258" s="6" t="n">
+      <c r="E258" s="2" t="n">
         <v>183169</v>
       </c>
-      <c r="F258" s="6" t="inlineStr">
+      <c r="F258" s="2" t="inlineStr">
         <is>
           <t>+2.3%</t>
         </is>
       </c>
-      <c r="G258" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H258" s="6" t="n"/>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="n"/>
     </row>
     <row r="259">
-      <c r="A259" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B259" s="6" t="inlineStr">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>2004-11-01</t>
         </is>
       </c>
-      <c r="C259" s="6" t="n">
+      <c r="C259" s="2" t="n">
         <v>8152569</v>
       </c>
-      <c r="D259" s="6" t="n">
+      <c r="D259" s="2" t="n">
         <v>7559250</v>
       </c>
-      <c r="E259" s="6" t="n">
+      <c r="E259" s="2" t="n">
         <v>593319</v>
       </c>
-      <c r="F259" s="6" t="inlineStr">
+      <c r="F259" s="2" t="inlineStr">
         <is>
           <t>+7.8%</t>
         </is>
       </c>
-      <c r="G259" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H259" s="6" t="n"/>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B260" s="6" t="inlineStr">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>2004-10-01</t>
         </is>
       </c>
-      <c r="C260" s="6" t="n">
+      <c r="C260" s="2" t="n">
         <v>8524930</v>
       </c>
-      <c r="D260" s="6" t="n">
+      <c r="D260" s="2" t="n">
         <v>8773115</v>
       </c>
-      <c r="E260" s="6" t="n">
+      <c r="E260" s="2" t="n">
         <v>-248185</v>
       </c>
-      <c r="F260" s="6" t="inlineStr">
+      <c r="F260" s="2" t="inlineStr">
         <is>
           <t>-2.8%</t>
         </is>
       </c>
-      <c r="G260" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H260" s="6" t="n"/>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="n"/>
     </row>
     <row r="261">
-      <c r="A261" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B261" s="6" t="inlineStr">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>2004-09-01</t>
         </is>
       </c>
-      <c r="C261" s="6" t="n">
+      <c r="C261" s="2" t="n">
         <v>8599271</v>
       </c>
-      <c r="D261" s="6" t="n">
+      <c r="D261" s="2" t="n">
         <v>8322915</v>
       </c>
-      <c r="E261" s="6" t="n">
+      <c r="E261" s="2" t="n">
         <v>276356</v>
       </c>
-      <c r="F261" s="6" t="inlineStr">
+      <c r="F261" s="2" t="inlineStr">
         <is>
           <t>+3.3%</t>
         </is>
       </c>
-      <c r="G261" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H261" s="6" t="n"/>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -25353,164 +25345,164 @@
       <c r="H262" s="3" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B263" s="6" t="inlineStr">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>2004-07-01</t>
         </is>
       </c>
-      <c r="C263" s="6" t="n">
+      <c r="C263" s="2" t="n">
         <v>8290098</v>
       </c>
-      <c r="D263" s="6" t="n">
+      <c r="D263" s="2" t="n">
         <v>8183386</v>
       </c>
-      <c r="E263" s="6" t="n">
+      <c r="E263" s="2" t="n">
         <v>106712</v>
       </c>
-      <c r="F263" s="6" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>+1.3%</t>
         </is>
       </c>
-      <c r="G263" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H263" s="6" t="n"/>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B264" s="6" t="inlineStr">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>2004-06-01</t>
         </is>
       </c>
-      <c r="C264" s="6" t="n">
+      <c r="C264" s="2" t="n">
         <v>8416224</v>
       </c>
-      <c r="D264" s="6" t="n">
+      <c r="D264" s="2" t="n">
         <v>7686622</v>
       </c>
-      <c r="E264" s="6" t="n">
+      <c r="E264" s="2" t="n">
         <v>729602</v>
       </c>
-      <c r="F264" s="6" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>+9.5%</t>
         </is>
       </c>
-      <c r="G264" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H264" s="6" t="n"/>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B265" s="6" t="inlineStr">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
         <is>
           <t>2004-05-01</t>
         </is>
       </c>
-      <c r="C265" s="6" t="n">
+      <c r="C265" s="2" t="n">
         <v>8224919</v>
       </c>
-      <c r="D265" s="6" t="n">
+      <c r="D265" s="2" t="n">
         <v>7770298</v>
       </c>
-      <c r="E265" s="6" t="n">
+      <c r="E265" s="2" t="n">
         <v>454621</v>
       </c>
-      <c r="F265" s="6" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>+5.9%</t>
         </is>
       </c>
-      <c r="G265" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H265" s="6" t="n"/>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="n"/>
     </row>
     <row r="266">
-      <c r="A266" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B266" s="6" t="inlineStr">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>2004-04-01</t>
         </is>
       </c>
-      <c r="C266" s="6" t="n">
+      <c r="C266" s="2" t="n">
         <v>8332090</v>
       </c>
-      <c r="D266" s="6" t="n">
+      <c r="D266" s="2" t="n">
         <v>7744429</v>
       </c>
-      <c r="E266" s="6" t="n">
+      <c r="E266" s="2" t="n">
         <v>587661</v>
       </c>
-      <c r="F266" s="6" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>+7.6%</t>
         </is>
       </c>
-      <c r="G266" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H266" s="6" t="n"/>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="n"/>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B267" s="6" t="inlineStr">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>2004-03-01</t>
         </is>
       </c>
-      <c r="C267" s="6" t="n">
+      <c r="C267" s="2" t="n">
         <v>8574110</v>
       </c>
-      <c r="D267" s="6" t="n">
+      <c r="D267" s="2" t="n">
         <v>7824583</v>
       </c>
-      <c r="E267" s="6" t="n">
+      <c r="E267" s="2" t="n">
         <v>749527</v>
       </c>
-      <c r="F267" s="6" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>+9.6%</t>
         </is>
       </c>
-      <c r="G267" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H267" s="6" t="n"/>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -25545,68 +25537,68 @@
       <c r="H268" s="3" t="n"/>
     </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B269" s="6" t="inlineStr">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
         <is>
           <t>2004-01-01</t>
         </is>
       </c>
-      <c r="C269" s="6" t="n">
+      <c r="C269" s="2" t="n">
         <v>7580822</v>
       </c>
-      <c r="D269" s="6" t="n">
+      <c r="D269" s="2" t="n">
         <v>7742974</v>
       </c>
-      <c r="E269" s="6" t="n">
+      <c r="E269" s="2" t="n">
         <v>-162152</v>
       </c>
-      <c r="F269" s="6" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>-2.1%</t>
         </is>
       </c>
-      <c r="G269" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H269" s="6" t="n"/>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="n"/>
     </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B270" s="6" t="inlineStr">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>2003-12-01</t>
         </is>
       </c>
-      <c r="C270" s="6" t="n">
+      <c r="C270" s="2" t="n">
         <v>7916215</v>
       </c>
-      <c r="D270" s="6" t="n">
+      <c r="D270" s="2" t="n">
         <v>7420142</v>
       </c>
-      <c r="E270" s="6" t="n">
+      <c r="E270" s="2" t="n">
         <v>496073</v>
       </c>
-      <c r="F270" s="6" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>+6.7%</t>
         </is>
       </c>
-      <c r="G270" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H270" s="6" t="n"/>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
@@ -25641,36 +25633,36 @@
       <c r="H271" s="4" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B272" s="6" t="inlineStr">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>2003-10-01</t>
         </is>
       </c>
-      <c r="C272" s="6" t="n">
+      <c r="C272" s="2" t="n">
         <v>8773115</v>
       </c>
-      <c r="D272" s="6" t="n">
+      <c r="D272" s="2" t="n">
         <v>8586941</v>
       </c>
-      <c r="E272" s="6" t="n">
+      <c r="E272" s="2" t="n">
         <v>186174</v>
       </c>
-      <c r="F272" s="6" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>+2.2%</t>
         </is>
       </c>
-      <c r="G272" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H272" s="6" t="n"/>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
@@ -25705,68 +25697,68 @@
       <c r="H273" s="4" t="n"/>
     </row>
     <row r="274">
-      <c r="A274" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B274" s="6" t="inlineStr">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>2003-08-01</t>
         </is>
       </c>
-      <c r="C274" s="6" t="n">
+      <c r="C274" s="2" t="n">
         <v>8187127</v>
       </c>
-      <c r="D274" s="6" t="n">
+      <c r="D274" s="2" t="n">
         <v>8102483</v>
       </c>
-      <c r="E274" s="6" t="n">
+      <c r="E274" s="2" t="n">
         <v>84644</v>
       </c>
-      <c r="F274" s="6" t="inlineStr">
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>+1.0%</t>
         </is>
       </c>
-      <c r="G274" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H274" s="6" t="n"/>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B275" s="6" t="inlineStr">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>2003-07-01</t>
         </is>
       </c>
-      <c r="C275" s="6" t="n">
+      <c r="C275" s="2" t="n">
         <v>8183386</v>
       </c>
-      <c r="D275" s="6" t="n">
+      <c r="D275" s="2" t="n">
         <v>8115480</v>
       </c>
-      <c r="E275" s="6" t="n">
+      <c r="E275" s="2" t="n">
         <v>67906</v>
       </c>
-      <c r="F275" s="6" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>+0.8%</t>
         </is>
       </c>
-      <c r="G275" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H275" s="6" t="n"/>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -25801,36 +25793,36 @@
       <c r="H276" s="3" t="n"/>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B277" s="6" t="inlineStr">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>2003-05-01</t>
         </is>
       </c>
-      <c r="C277" s="6" t="n">
+      <c r="C277" s="2" t="n">
         <v>7770298</v>
       </c>
-      <c r="D277" s="6" t="n">
+      <c r="D277" s="2" t="n">
         <v>8289133</v>
       </c>
-      <c r="E277" s="6" t="n">
+      <c r="E277" s="2" t="n">
         <v>-518835</v>
       </c>
-      <c r="F277" s="6" t="inlineStr">
+      <c r="F277" s="2" t="inlineStr">
         <is>
           <t>-6.3%</t>
         </is>
       </c>
-      <c r="G277" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H277" s="6" t="n"/>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -25985,28 +25977,28 @@
       <c r="H282" s="3" t="n"/>
     </row>
     <row r="283">
-      <c r="A283" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B283" s="6" t="inlineStr">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>2002-11-01</t>
         </is>
       </c>
-      <c r="C283" s="6" t="n">
+      <c r="C283" s="2" t="n">
         <v>7426050</v>
       </c>
-      <c r="D283" s="6" t="n"/>
-      <c r="E283" s="6" t="n"/>
-      <c r="F283" s="6" t="inlineStr"/>
-      <c r="G283" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H283" s="6" t="n"/>
+      <c r="D283" s="2" t="n"/>
+      <c r="E283" s="2" t="n"/>
+      <c r="F283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -26129,124 +26121,124 @@
       <c r="H288" s="3" t="n"/>
     </row>
     <row r="289">
-      <c r="A289" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B289" s="6" t="inlineStr">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
         <is>
           <t>2002-05-01</t>
         </is>
       </c>
-      <c r="C289" s="6" t="n">
+      <c r="C289" s="2" t="n">
         <v>8289133</v>
       </c>
-      <c r="D289" s="6" t="n"/>
-      <c r="E289" s="6" t="n"/>
-      <c r="F289" s="6" t="inlineStr"/>
-      <c r="G289" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H289" s="6" t="n"/>
+      <c r="D289" s="2" t="n"/>
+      <c r="E289" s="2" t="n"/>
+      <c r="F289" s="2" t="inlineStr"/>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="n"/>
     </row>
     <row r="290">
-      <c r="A290" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B290" s="6" t="inlineStr">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
         <is>
           <t>2002-04-01</t>
         </is>
       </c>
-      <c r="C290" s="6" t="n">
+      <c r="C290" s="2" t="n">
         <v>8270355</v>
       </c>
-      <c r="D290" s="6" t="n"/>
-      <c r="E290" s="6" t="n"/>
-      <c r="F290" s="6" t="inlineStr"/>
-      <c r="G290" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H290" s="6" t="n"/>
+      <c r="D290" s="2" t="n"/>
+      <c r="E290" s="2" t="n"/>
+      <c r="F290" s="2" t="inlineStr"/>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="n"/>
     </row>
     <row r="291">
-      <c r="A291" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B291" s="6" t="inlineStr">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
         <is>
           <t>2002-03-01</t>
         </is>
       </c>
-      <c r="C291" s="6" t="n">
+      <c r="C291" s="2" t="n">
         <v>7964285</v>
       </c>
-      <c r="D291" s="6" t="n"/>
-      <c r="E291" s="6" t="n"/>
-      <c r="F291" s="6" t="inlineStr"/>
-      <c r="G291" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H291" s="6" t="n"/>
+      <c r="D291" s="2" t="n"/>
+      <c r="E291" s="2" t="n"/>
+      <c r="F291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="n"/>
     </row>
     <row r="292">
-      <c r="A292" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B292" s="6" t="inlineStr">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
         <is>
           <t>2002-02-01</t>
         </is>
       </c>
-      <c r="C292" s="6" t="n">
+      <c r="C292" s="2" t="n">
         <v>7345194</v>
       </c>
-      <c r="D292" s="6" t="n"/>
-      <c r="E292" s="6" t="n"/>
-      <c r="F292" s="6" t="inlineStr"/>
-      <c r="G292" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H292" s="6" t="n"/>
+      <c r="D292" s="2" t="n"/>
+      <c r="E292" s="2" t="n"/>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="n"/>
     </row>
     <row r="293">
-      <c r="A293" s="6" t="inlineStr">
-        <is>
-          <t>Bay Area Rapid Transit</t>
-        </is>
-      </c>
-      <c r="B293" s="6" t="inlineStr">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Bay Area Rapid Transit</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
         <is>
           <t>2002-01-01</t>
         </is>
       </c>
-      <c r="C293" s="6" t="n">
+      <c r="C293" s="2" t="n">
         <v>7909547</v>
       </c>
-      <c r="D293" s="6" t="n"/>
-      <c r="E293" s="6" t="n"/>
-      <c r="F293" s="6" t="inlineStr"/>
-      <c r="G293" s="6" t="inlineStr">
-        <is>
-          <t>NTD</t>
-        </is>
-      </c>
-      <c r="H293" s="6" t="n"/>
+      <c r="D293" s="2" t="n"/>
+      <c r="E293" s="2" t="n"/>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>NTD</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26267,210 +26259,210 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>BCN Transit Tracker — Bay City News</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>Last updated: May 02, 2026 at 19:58 UTC</t>
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Last updated: May 02, 2026 at 20:30 UTC</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr"/>
+      <c r="A3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>START HERE: Open the Summary tab. It tells you what's notable in plain language.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr"/>
+      <c r="A5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>TABS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Plain-language flags. Green = strong growth. Red = decline. Start here.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Master</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Full dataset — every month, every agency. All sources and QA flags.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Monthly Pivot</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Wide format — one row per agency, columns are months. Good for quick scans.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Year-over-Year</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>% change vs same month last year. Green = up &gt;5%, Red = down &gt;5%.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ReadMe</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>This tab.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr"/>
+      <c r="A12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>DATA FLAGS</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>(blank)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Variance between agency and NTD is under 5% — normal.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>5–10% variance. Worth a look before publishing.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>INVESTIGATE</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Over 10% variance. Do not publish without understanding the difference.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>is_provisional</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Partial month estimate. Numbers will change when month completes.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr"/>
+      <c r="A18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>bart.gov</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>BART daily paid exits. Scraped automatically each weekday at 6 AM PT.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>NTD Monthly</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>National Transit Database. ~2 month lag. Adjusted and finalized.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr"/>
+      <c r="A22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>CONTACT</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Andres Jimenez Larios | Bay City News</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>GitHub: https://github.com/alariosjx/bcn-transit-tracker</t>
         </is>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -26282,7 +26282,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Last updated: May 02, 2026 at 20:58 UTC</t>
+          <t>Last updated: May 02, 2026 at 21:03 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13737,7 +13737,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:43Z</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14819,7 +14819,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15371,7 +15371,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16705,7 +16705,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17119,7 +17119,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17487,7 +17487,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17625,7 +17625,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17947,7 +17947,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18223,7 +18223,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18361,7 +18361,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18407,7 +18407,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18775,7 +18775,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19005,7 +19005,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19281,7 +19281,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19465,7 +19465,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19557,7 +19557,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19925,7 +19925,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20247,7 +20247,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20339,7 +20339,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20799,7 +20799,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20891,7 +20891,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21029,7 +21029,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21351,7 +21351,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21397,7 +21397,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21443,7 +21443,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21673,7 +21673,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21719,7 +21719,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21765,7 +21765,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21811,7 +21811,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -21995,7 +21995,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22087,7 +22087,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22133,7 +22133,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22271,7 +22271,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22317,7 +22317,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22363,7 +22363,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22501,7 +22501,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22547,7 +22547,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22639,7 +22639,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22731,7 +22731,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22915,7 +22915,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -22961,7 +22961,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23145,7 +23145,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23237,7 +23237,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23283,7 +23283,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23329,7 +23329,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23467,7 +23467,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23651,7 +23651,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23789,7 +23789,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23881,7 +23881,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24019,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24203,7 +24203,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24249,7 +24249,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24295,7 +24295,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24441,7 +24441,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24491,7 +24491,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24541,7 +24541,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24691,7 +24691,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24791,7 +24791,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24841,7 +24841,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24941,7 +24941,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25041,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25091,7 +25091,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25191,7 +25191,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25291,7 +25291,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25391,7 +25391,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25491,7 +25491,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25541,7 +25541,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25591,7 +25591,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25641,7 +25641,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25691,7 +25691,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25741,7 +25741,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25791,7 +25791,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26041,7 +26041,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26141,7 +26141,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26241,7 +26241,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26341,7 +26341,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26591,7 +26591,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26641,7 +26641,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26741,7 +26741,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26791,7 +26791,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26841,7 +26841,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26941,7 +26941,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27091,7 +27091,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27141,7 +27141,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27191,7 +27191,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27291,7 +27291,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27341,7 +27341,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27391,7 +27391,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27441,7 +27441,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27491,7 +27491,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27541,7 +27541,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27591,7 +27591,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27641,7 +27641,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27691,7 +27691,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27791,7 +27791,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27891,7 +27891,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -27941,7 +27941,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T21:52:44Z</t>
         </is>
       </c>
     </row>
@@ -50103,7 +50103,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 02, 2026 at 21:49 UTC</t>
+          <t>Last updated: May 02, 2026 at 21:52 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13737,7 +13737,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14819,7 +14819,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15371,7 +15371,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16705,7 +16705,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17119,7 +17119,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17487,7 +17487,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17625,7 +17625,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17947,7 +17947,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18223,7 +18223,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18361,7 +18361,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18407,7 +18407,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18775,7 +18775,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19005,7 +19005,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19281,7 +19281,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19465,7 +19465,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19557,7 +19557,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19925,7 +19925,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20247,7 +20247,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20339,7 +20339,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20799,7 +20799,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20891,7 +20891,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21029,7 +21029,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21351,7 +21351,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21397,7 +21397,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21443,7 +21443,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21673,7 +21673,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21719,7 +21719,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21765,7 +21765,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21811,7 +21811,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -21995,7 +21995,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22087,7 +22087,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22133,7 +22133,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22271,7 +22271,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22317,7 +22317,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22363,7 +22363,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22501,7 +22501,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22547,7 +22547,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22639,7 +22639,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22731,7 +22731,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22915,7 +22915,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -22961,7 +22961,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23145,7 +23145,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23237,7 +23237,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23283,7 +23283,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23329,7 +23329,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23467,7 +23467,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23651,7 +23651,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23789,7 +23789,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23881,7 +23881,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24019,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24203,7 +24203,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24249,7 +24249,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24295,7 +24295,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24441,7 +24441,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24491,7 +24491,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24541,7 +24541,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24691,7 +24691,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24791,7 +24791,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24841,7 +24841,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24941,7 +24941,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25041,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25091,7 +25091,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25191,7 +25191,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25291,7 +25291,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25391,7 +25391,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25491,7 +25491,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25541,7 +25541,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25591,7 +25591,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25641,7 +25641,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25691,7 +25691,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25741,7 +25741,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25791,7 +25791,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26041,7 +26041,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26141,7 +26141,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26241,7 +26241,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26341,7 +26341,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26591,7 +26591,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26641,7 +26641,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26741,7 +26741,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26791,7 +26791,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26841,7 +26841,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26941,7 +26941,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27091,7 +27091,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27141,7 +27141,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27191,7 +27191,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27291,7 +27291,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27341,7 +27341,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27391,7 +27391,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27441,7 +27441,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:06:59Z</t>
         </is>
       </c>
     </row>
@@ -27491,7 +27491,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27541,7 +27541,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27591,7 +27591,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27641,7 +27641,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27691,7 +27691,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27791,7 +27791,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27891,7 +27891,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -27941,7 +27941,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T21:49:17Z</t>
+          <t>2026-05-02T22:07:00Z</t>
         </is>
       </c>
     </row>
@@ -50103,7 +50103,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 02, 2026 at 21:49 UTC</t>
+          <t>Last updated: May 02, 2026 at 22:10 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -500,7 +500,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="39" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -621,7 +621,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>109.9% of Mar 2019 (13,548,774 baseline)</t>
+          <t>84.4% of Mar 2019 (17,642,000 SFMTA baseline)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -50086,7 +50086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -50103,7 +50103,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 02, 2026 at 22:10 UTC</t>
+          <t>Last updated: May 02, 2026 at 22:20 UTC</t>
         </is>
       </c>
     </row>
@@ -50270,34 +50270,80 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
+          <t>sfmta.com</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Muni total boardings. Scraped automatically each weekday at 6 AM PT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
           <t>NTD Monthly</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>National Transit Database. ~2 month lag. Adjusted and finalized.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>CONTACT</t>
-        </is>
-      </c>
+      <c r="A23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Andres Jimenez Larios | Bay City News</t>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Muni recovery %</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Uses SFMTA's own 2019 baseline — methodology matches SFMTA reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>BART recovery %</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Uses NTD 2019 same-month as baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>CONTACT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Andres Jimenez Larios | Bay City News</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>GitHub: https://github.com/alariosjx/bcn-transit-tracker</t>
         </is>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -50103,7 +50103,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 02, 2026 at 22:20 UTC</t>
+          <t>Last updated: May 03, 2026 at 22:04 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -763,7 +763,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13467,7 +13467,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13737,7 +13737,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13845,7 +13845,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -14007,7 +14007,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -14115,7 +14115,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14267,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:11Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14451,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14819,7 +14819,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -14957,7 +14957,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15233,7 +15233,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15371,7 +15371,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16475,7 +16475,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16705,7 +16705,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16843,7 +16843,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17119,7 +17119,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17211,7 +17211,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17487,7 +17487,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17625,7 +17625,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17671,7 +17671,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17763,7 +17763,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17947,7 +17947,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18039,7 +18039,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18085,7 +18085,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18177,7 +18177,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18223,7 +18223,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18315,7 +18315,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18361,7 +18361,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18407,7 +18407,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18499,7 +18499,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18775,7 +18775,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19005,7 +19005,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19143,7 +19143,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19281,7 +19281,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19373,7 +19373,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19419,7 +19419,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19465,7 +19465,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19557,7 +19557,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19603,7 +19603,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19649,7 +19649,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19925,7 +19925,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -19971,7 +19971,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20247,7 +20247,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20293,7 +20293,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20339,7 +20339,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20569,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20799,7 +20799,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20891,7 +20891,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -20983,7 +20983,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21029,7 +21029,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21075,7 +21075,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21121,7 +21121,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21167,7 +21167,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21213,7 +21213,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21259,7 +21259,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21305,7 +21305,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21351,7 +21351,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21397,7 +21397,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21443,7 +21443,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21535,7 +21535,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21673,7 +21673,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21719,7 +21719,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21765,7 +21765,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21811,7 +21811,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21857,7 +21857,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21949,7 +21949,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -21995,7 +21995,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22087,7 +22087,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22133,7 +22133,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22179,7 +22179,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22225,7 +22225,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22271,7 +22271,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22317,7 +22317,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22363,7 +22363,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22455,7 +22455,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22501,7 +22501,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22547,7 +22547,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22639,7 +22639,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22685,7 +22685,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22731,7 +22731,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22777,7 +22777,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22915,7 +22915,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -22961,7 +22961,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23099,7 +23099,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23145,7 +23145,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23237,7 +23237,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23283,7 +23283,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23329,7 +23329,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23421,7 +23421,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23467,7 +23467,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23513,7 +23513,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23651,7 +23651,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23789,7 +23789,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23881,7 +23881,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23927,7 +23927,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -23973,7 +23973,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24019,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24157,7 +24157,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24203,7 +24203,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24249,7 +24249,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24295,7 +24295,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24441,7 +24441,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24491,7 +24491,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24541,7 +24541,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24691,7 +24691,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24791,7 +24791,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24841,7 +24841,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24891,7 +24891,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24941,7 +24941,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -24991,7 +24991,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25041,7 +25041,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25091,7 +25091,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25141,7 +25141,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25191,7 +25191,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25291,7 +25291,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25341,7 +25341,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25391,7 +25391,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25491,7 +25491,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25541,7 +25541,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25591,7 +25591,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25641,7 +25641,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25691,7 +25691,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25741,7 +25741,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25791,7 +25791,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25941,7 +25941,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26041,7 +26041,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26091,7 +26091,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26141,7 +26141,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26191,7 +26191,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26241,7 +26241,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26341,7 +26341,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26591,7 +26591,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26641,7 +26641,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26741,7 +26741,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26791,7 +26791,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26841,7 +26841,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26891,7 +26891,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26941,7 +26941,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27091,7 +27091,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27141,7 +27141,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27191,7 +27191,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27291,7 +27291,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27341,7 +27341,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27391,7 +27391,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27441,7 +27441,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:06:59Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27491,7 +27491,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27541,7 +27541,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27591,7 +27591,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27641,7 +27641,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27691,7 +27691,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27741,7 +27741,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27791,7 +27791,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27841,7 +27841,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27891,7 +27891,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -27941,7 +27941,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-02T22:07:00Z</t>
+          <t>2026-05-04T15:56:12Z</t>
         </is>
       </c>
     </row>
@@ -50103,7 +50103,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 03, 2026 at 22:04 UTC</t>
+          <t>Last updated: May 04, 2026 at 15:56 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:32Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
         </is>
       </c>
       <c r="F294" s="4" t="n">
-        <v>374488</v>
+        <v>560757</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18543,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19095,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22499,7 +22499,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23005,7 +23005,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23143,7 +23143,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23189,7 +23189,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23695,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:33Z</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24581,7 +24581,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24781,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25081,7 +25081,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25131,7 +25131,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25631,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25831,7 +25831,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25881,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -25981,7 +25981,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26531,7 +26531,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27481,7 +27481,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27631,7 +27631,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27731,7 +27731,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="L585" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="L587" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28177,7 +28177,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="L589" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="L591" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28477,7 +28477,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="L595" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28577,7 +28577,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="L597" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="L599" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="L601" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L603" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="L605" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="L607" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29227,7 +29227,7 @@
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29377,7 +29377,7 @@
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="L615" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="L617" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29727,7 +29727,7 @@
       </c>
       <c r="L619" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29827,7 @@
       </c>
       <c r="L621" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29877,7 +29877,7 @@
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="L625" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="L627" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30227,7 +30227,7 @@
       </c>
       <c r="L629" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30327,7 +30327,7 @@
       </c>
       <c r="L631" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30377,7 +30377,7 @@
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="L633" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30477,7 +30477,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="L635" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="L637" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30677,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="L639" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30777,7 +30777,7 @@
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="L641" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="L644" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31027,7 +31027,7 @@
       </c>
       <c r="L645" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="L646" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="L647" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31177,7 +31177,7 @@
       </c>
       <c r="L648" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="L649" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31327,7 +31327,7 @@
       </c>
       <c r="L651" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31377,7 @@
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="L655" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="L657" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31727,7 +31727,7 @@
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="L661" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="L663" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="L665" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32077,7 +32077,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32127,7 +32127,7 @@
       </c>
       <c r="L667" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32227,7 @@
       </c>
       <c r="L669" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="L671" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32377,7 @@
       </c>
       <c r="L672" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="L673" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="L674" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L675" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="L676" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32677,7 @@
       </c>
       <c r="L678" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32727,7 +32727,7 @@
       </c>
       <c r="L679" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="L680" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="L681" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32877,7 +32877,7 @@
       </c>
       <c r="L682" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32927,7 @@
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="L684" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33027,7 @@
       </c>
       <c r="L685" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="L686" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="L687" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="L688" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -33227,7 +33227,7 @@
       </c>
       <c r="L689" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="L690" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T05:18:35Z</t>
+          <t>2026-05-05T17:46:34Z</t>
         </is>
       </c>
     </row>
@@ -59212,7 +59212,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 05, 2026 at 05:31 UTC</t>
+          <t>Last updated: May 05, 2026 at 17:46 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:32Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18543,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19095,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22499,7 +22499,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23005,7 +23005,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23143,7 +23143,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23189,7 +23189,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23695,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:03Z</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:33Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24581,7 +24581,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24781,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25081,7 +25081,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25131,7 +25131,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25631,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25831,7 +25831,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25881,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -25981,7 +25981,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26531,7 +26531,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27481,7 +27481,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27631,7 +27631,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27731,7 +27731,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="L585" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="L587" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28177,7 +28177,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="L589" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="L591" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28477,7 +28477,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="L595" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28577,7 +28577,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="L597" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="L599" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="L601" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L603" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="L605" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="L607" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29227,7 +29227,7 @@
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29377,7 +29377,7 @@
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="L615" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="L617" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29727,7 +29727,7 @@
       </c>
       <c r="L619" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29827,7 @@
       </c>
       <c r="L621" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29877,7 +29877,7 @@
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="L625" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="L627" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30227,7 +30227,7 @@
       </c>
       <c r="L629" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30327,7 +30327,7 @@
       </c>
       <c r="L631" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30377,7 +30377,7 @@
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="L633" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30477,7 +30477,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="L635" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="L637" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30677,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="L639" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30777,7 +30777,7 @@
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="L641" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="L644" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31027,7 +31027,7 @@
       </c>
       <c r="L645" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="L646" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="L647" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31177,7 +31177,7 @@
       </c>
       <c r="L648" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="L649" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31327,7 +31327,7 @@
       </c>
       <c r="L651" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31377,7 @@
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="L655" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="L657" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31727,7 +31727,7 @@
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="L661" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="L663" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="L665" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32077,7 +32077,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32127,7 +32127,7 @@
       </c>
       <c r="L667" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32227,7 @@
       </c>
       <c r="L669" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="L671" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32377,7 @@
       </c>
       <c r="L672" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="L673" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="L674" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L675" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="L676" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32677,7 @@
       </c>
       <c r="L678" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32727,7 +32727,7 @@
       </c>
       <c r="L679" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="L680" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="L681" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32877,7 +32877,7 @@
       </c>
       <c r="L682" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32927,7 @@
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="L684" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33027,7 @@
       </c>
       <c r="L685" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="L686" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="L687" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="L688" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -33227,7 +33227,7 @@
       </c>
       <c r="L689" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="L690" s="4" t="inlineStr">
         <is>
-          <t>2026-05-05T17:46:34Z</t>
+          <t>2026-05-06T15:58:04Z</t>
         </is>
       </c>
     </row>
@@ -59212,7 +59212,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 05, 2026 at 17:46 UTC</t>
+          <t>Last updated: May 06, 2026 at 15:58 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:07Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
         </is>
       </c>
       <c r="F294" s="4" t="n">
-        <v>560757</v>
+        <v>1007898</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18543,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19095,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22499,7 +22499,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23005,7 +23005,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23143,7 +23143,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23189,7 +23189,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23695,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:03Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24581,7 +24581,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24781,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25081,7 +25081,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25131,7 +25131,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25631,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25831,7 +25831,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25881,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -25981,7 +25981,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26531,7 +26531,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27481,7 +27481,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27631,7 +27631,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27731,7 +27731,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="L585" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="L587" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28177,7 +28177,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="L589" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="L591" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28477,7 +28477,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="L595" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28577,7 +28577,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="L597" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="L599" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="L601" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L603" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="L605" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="L607" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29227,7 +29227,7 @@
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29377,7 +29377,7 @@
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="L615" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="L617" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29727,7 +29727,7 @@
       </c>
       <c r="L619" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29827,7 @@
       </c>
       <c r="L621" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29877,7 +29877,7 @@
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="L625" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="L627" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30227,7 +30227,7 @@
       </c>
       <c r="L629" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30327,7 +30327,7 @@
       </c>
       <c r="L631" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30377,7 +30377,7 @@
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="L633" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30477,7 +30477,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="L635" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="L637" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30677,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="L639" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30777,7 +30777,7 @@
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="L641" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="L644" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -31027,7 +31027,7 @@
       </c>
       <c r="L645" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="L646" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="L647" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:08Z</t>
         </is>
       </c>
     </row>
@@ -31177,7 +31177,7 @@
       </c>
       <c r="L648" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="L649" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31327,7 +31327,7 @@
       </c>
       <c r="L651" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31377,7 @@
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="L655" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="L657" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31727,7 +31727,7 @@
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="L661" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="L663" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="L665" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32077,7 +32077,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32127,7 +32127,7 @@
       </c>
       <c r="L667" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32227,7 @@
       </c>
       <c r="L669" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="L671" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32377,7 @@
       </c>
       <c r="L672" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="L673" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="L674" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L675" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="L676" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32677,7 @@
       </c>
       <c r="L678" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32727,7 +32727,7 @@
       </c>
       <c r="L679" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="L680" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="L681" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32877,7 +32877,7 @@
       </c>
       <c r="L682" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32927,7 @@
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="L684" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33027,7 @@
       </c>
       <c r="L685" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="L686" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="L687" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="L688" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -33227,7 +33227,7 @@
       </c>
       <c r="L689" s="5" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="L690" s="4" t="inlineStr">
         <is>
-          <t>2026-05-06T15:58:04Z</t>
+          <t>2026-05-07T16:00:09Z</t>
         </is>
       </c>
     </row>
@@ -59212,7 +59212,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 06, 2026 at 15:58 UTC</t>
+          <t>Last updated: May 07, 2026 at 16:00 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>5,233,814</t>
+          <t>5,250,519</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -573,22 +573,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>▲ 10.5% vs Apr 2025 (4,736,423 → 5,233,814)</t>
+          <t>▲ 10.9% vs Apr 2025 (4,736,423 → 5,250,519)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>▼ 3.1% vs Mar 2026 (5,403,169 → 5,233,814)</t>
+          <t>▼ 2.8% vs Mar 2026 (5,403,169 → 5,250,519)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>48.6% of Apr 2019 (10,779,665 baseline)</t>
+          <t>48.7% of Apr 2019 (10,779,665 baseline)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Strong growth year-over-year (+10.5%)</t>
+          <t>Strong growth year-over-year (+10.9%)</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>▲ 8.2% vs Mar 2025 (13,761,000 → 14,883,000)</t>
+          <t>▲ 7.8% vs Mar 2025 (13,810,000 → 14,883,000)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:07Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="F293" s="5" t="n">
-        <v>5233814</v>
+        <v>5250519</v>
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
         </is>
       </c>
       <c r="F294" s="4" t="n">
-        <v>1007898</v>
+        <v>1629743</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:10Z</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18543,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19095,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22499,7 +22499,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23005,7 +23005,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23143,7 +23143,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23189,7 +23189,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23695,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24581,7 +24581,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24781,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25081,7 +25081,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25131,7 +25131,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25631,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25831,7 +25831,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25881,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -25981,7 +25981,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26110,7 +26110,7 @@
         </is>
       </c>
       <c r="F547" s="5" t="n">
-        <v>10610000</v>
+        <v>10664000</v>
       </c>
       <c r="G547" s="5" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
       </c>
       <c r="I547" s="5" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="J547" s="5" t="n"/>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26160,7 +26160,7 @@
         </is>
       </c>
       <c r="F548" s="4" t="n">
-        <v>10590000</v>
+        <v>10648000</v>
       </c>
       <c r="G548" s="4" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="I548" s="4" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="J548" s="4" t="n"/>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26210,7 +26210,7 @@
         </is>
       </c>
       <c r="F549" s="5" t="n">
-        <v>11775000</v>
+        <v>11856000</v>
       </c>
       <c r="G549" s="5" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
       </c>
       <c r="I549" s="5" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J549" s="5" t="n"/>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26260,7 +26260,7 @@
         </is>
       </c>
       <c r="F550" s="4" t="n">
-        <v>12127000</v>
+        <v>12192000</v>
       </c>
       <c r="G550" s="4" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
       </c>
       <c r="I550" s="4" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J550" s="4" t="n"/>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26310,7 +26310,7 @@
         </is>
       </c>
       <c r="F551" s="5" t="n">
-        <v>12550000</v>
+        <v>12608000</v>
       </c>
       <c r="G551" s="5" t="inlineStr">
         <is>
@@ -26322,7 +26322,7 @@
       </c>
       <c r="I551" s="5" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J551" s="5" t="n"/>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26360,7 +26360,7 @@
         </is>
       </c>
       <c r="F552" s="4" t="n">
-        <v>11857000</v>
+        <v>11920000</v>
       </c>
       <c r="G552" s="4" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
       </c>
       <c r="I552" s="4" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="J552" s="4" t="n"/>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
         </is>
       </c>
       <c r="F553" s="5" t="n">
-        <v>12049000</v>
+        <v>12103000</v>
       </c>
       <c r="G553" s="5" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
       </c>
       <c r="I553" s="5" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="J553" s="5" t="n"/>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26460,7 +26460,7 @@
         </is>
       </c>
       <c r="F554" s="4" t="n">
-        <v>13266000</v>
+        <v>13322000</v>
       </c>
       <c r="G554" s="4" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
       </c>
       <c r="I554" s="4" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="J554" s="4" t="n"/>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26510,7 +26510,7 @@
         </is>
       </c>
       <c r="F555" s="5" t="n">
-        <v>13019000</v>
+        <v>13079000</v>
       </c>
       <c r="G555" s="5" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
       </c>
       <c r="I555" s="5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J555" s="5" t="n"/>
@@ -26531,7 +26531,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26560,7 +26560,7 @@
         </is>
       </c>
       <c r="F556" s="4" t="n">
-        <v>13405000</v>
+        <v>13470000</v>
       </c>
       <c r="G556" s="4" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
       </c>
       <c r="I556" s="4" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="J556" s="4" t="n"/>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26610,7 +26610,7 @@
         </is>
       </c>
       <c r="F557" s="5" t="n">
-        <v>11959000</v>
+        <v>12020000</v>
       </c>
       <c r="G557" s="5" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
       </c>
       <c r="I557" s="5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="J557" s="5" t="n"/>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26660,7 +26660,7 @@
         </is>
       </c>
       <c r="F558" s="4" t="n">
-        <v>11795000</v>
+        <v>11848000</v>
       </c>
       <c r="G558" s="4" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
       </c>
       <c r="I558" s="4" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="J558" s="4" t="n"/>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26710,7 +26710,7 @@
         </is>
       </c>
       <c r="F559" s="5" t="n">
-        <v>12246000</v>
+        <v>12309000</v>
       </c>
       <c r="G559" s="5" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
       </c>
       <c r="I559" s="5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="J559" s="5" t="n"/>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26760,7 +26760,7 @@
         </is>
       </c>
       <c r="F560" s="4" t="n">
-        <v>12234000</v>
+        <v>12298000</v>
       </c>
       <c r="G560" s="4" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
       </c>
       <c r="I560" s="4" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J560" s="4" t="n"/>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26810,7 +26810,7 @@
         </is>
       </c>
       <c r="F561" s="5" t="n">
-        <v>13384000</v>
+        <v>13454000</v>
       </c>
       <c r="G561" s="5" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="I561" s="5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="J561" s="5" t="n"/>
@@ -26831,7 +26831,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="F562" s="4" t="n">
-        <v>13179000</v>
+        <v>13242000</v>
       </c>
       <c r="G562" s="4" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
       </c>
       <c r="I562" s="4" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="J562" s="4" t="n"/>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26910,7 +26910,7 @@
         </is>
       </c>
       <c r="F563" s="5" t="n">
-        <v>13903000</v>
+        <v>13970000</v>
       </c>
       <c r="G563" s="5" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="I563" s="5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J563" s="5" t="n"/>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -26960,7 +26960,7 @@
         </is>
       </c>
       <c r="F564" s="4" t="n">
-        <v>12665000</v>
+        <v>12729000</v>
       </c>
       <c r="G564" s="4" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="I564" s="4" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J564" s="4" t="n"/>
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27010,7 +27010,7 @@
         </is>
       </c>
       <c r="F565" s="5" t="n">
-        <v>13085000</v>
+        <v>13138000</v>
       </c>
       <c r="G565" s="5" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
       </c>
       <c r="I565" s="5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="J565" s="5" t="n"/>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="F566" s="4" t="n">
-        <v>13790000</v>
+        <v>13870000</v>
       </c>
       <c r="G566" s="4" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
       </c>
       <c r="I566" s="4" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="J566" s="4" t="n"/>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
         </is>
       </c>
       <c r="F567" s="5" t="n">
-        <v>13957000</v>
+        <v>14027000</v>
       </c>
       <c r="G567" s="5" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
       </c>
       <c r="I567" s="5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="J567" s="5" t="n"/>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27160,7 +27160,7 @@
         </is>
       </c>
       <c r="F568" s="4" t="n">
-        <v>14788000</v>
+        <v>14860000</v>
       </c>
       <c r="G568" s="4" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
       </c>
       <c r="I568" s="4" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J568" s="4" t="n"/>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27210,7 +27210,7 @@
         </is>
       </c>
       <c r="F569" s="5" t="n">
-        <v>12586000</v>
+        <v>12643000</v>
       </c>
       <c r="G569" s="5" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
       </c>
       <c r="I569" s="5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="J569" s="5" t="n"/>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27260,7 @@
         </is>
       </c>
       <c r="F570" s="4" t="n">
-        <v>12527000</v>
+        <v>12590000</v>
       </c>
       <c r="G570" s="4" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
       </c>
       <c r="I570" s="4" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="J570" s="4" t="n"/>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27310,7 +27310,7 @@
         </is>
       </c>
       <c r="F571" s="5" t="n">
-        <v>13292000</v>
+        <v>13352000</v>
       </c>
       <c r="G571" s="5" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="I571" s="5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="J571" s="5" t="n"/>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27360,7 +27360,7 @@
         </is>
       </c>
       <c r="F572" s="4" t="n">
-        <v>12263000</v>
+        <v>12305000</v>
       </c>
       <c r="G572" s="4" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
       </c>
       <c r="I572" s="4" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="J572" s="4" t="n"/>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27410,7 +27410,7 @@
         </is>
       </c>
       <c r="F573" s="5" t="n">
-        <v>13761000</v>
+        <v>13810000</v>
       </c>
       <c r="G573" s="5" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
       </c>
       <c r="I573" s="5" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="J573" s="5" t="n"/>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27460,7 +27460,7 @@
         </is>
       </c>
       <c r="F574" s="4" t="n">
-        <v>14066000</v>
+        <v>14120000</v>
       </c>
       <c r="G574" s="4" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
       </c>
       <c r="I574" s="4" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J574" s="4" t="n"/>
@@ -27481,7 +27481,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27510,7 +27510,7 @@
         </is>
       </c>
       <c r="F575" s="5" t="n">
-        <v>14427000</v>
+        <v>14488000</v>
       </c>
       <c r="G575" s="5" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
       </c>
       <c r="I575" s="5" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="J575" s="5" t="n"/>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27631,7 +27631,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27731,7 +27731,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="L585" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="L587" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28177,7 +28177,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="L589" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="L591" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28477,7 +28477,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="L595" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28577,7 +28577,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="L597" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="L599" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="L601" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L603" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="L605" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="L607" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29227,7 +29227,7 @@
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29377,7 +29377,7 @@
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="L615" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="L617" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29727,7 +29727,7 @@
       </c>
       <c r="L619" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29827,7 @@
       </c>
       <c r="L621" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29877,7 +29877,7 @@
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="L625" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="L627" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30227,7 +30227,7 @@
       </c>
       <c r="L629" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30327,7 +30327,7 @@
       </c>
       <c r="L631" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30377,7 +30377,7 @@
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="L633" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30477,7 +30477,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="L635" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="L637" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30677,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="L639" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30777,7 +30777,7 @@
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="L641" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="L644" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31027,7 +31027,7 @@
       </c>
       <c r="L645" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="L646" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="L647" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:08Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31177,7 +31177,7 @@
       </c>
       <c r="L648" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="L649" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31327,7 +31327,7 @@
       </c>
       <c r="L651" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31377,7 @@
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="L655" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="L657" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31727,7 +31727,7 @@
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="L661" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="L663" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="L665" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32077,7 +32077,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32127,7 +32127,7 @@
       </c>
       <c r="L667" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32227,7 @@
       </c>
       <c r="L669" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="L671" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32377,7 @@
       </c>
       <c r="L672" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="L673" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="L674" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L675" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="L676" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32677,7 @@
       </c>
       <c r="L678" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32727,7 +32727,7 @@
       </c>
       <c r="L679" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="L680" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="L681" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32877,7 +32877,7 @@
       </c>
       <c r="L682" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32927,7 @@
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="L684" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33027,7 @@
       </c>
       <c r="L685" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="L686" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="L687" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="L688" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -33227,7 +33227,7 @@
       </c>
       <c r="L689" s="5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="L690" s="4" t="inlineStr">
         <is>
-          <t>2026-05-07T16:00:09Z</t>
+          <t>2026-05-12T16:15:11Z</t>
         </is>
       </c>
     </row>
@@ -35064,7 +35064,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>5233814</v>
+        <v>5250519</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>5403169</v>
@@ -35978,91 +35978,91 @@
         <v>13175000</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>14427000</v>
+        <v>14488000</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>14066000</v>
+        <v>14120000</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>13761000</v>
+        <v>13810000</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>12263000</v>
+        <v>12305000</v>
       </c>
       <c r="Q3" s="5" t="n">
-        <v>13292000</v>
+        <v>13352000</v>
       </c>
       <c r="R3" s="5" t="n">
-        <v>12527000</v>
+        <v>12590000</v>
       </c>
       <c r="S3" s="5" t="n">
-        <v>12586000</v>
+        <v>12643000</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>14788000</v>
+        <v>14860000</v>
       </c>
       <c r="U3" s="5" t="n">
-        <v>13957000</v>
+        <v>14027000</v>
       </c>
       <c r="V3" s="5" t="n">
-        <v>13790000</v>
+        <v>13870000</v>
       </c>
       <c r="W3" s="5" t="n">
-        <v>13085000</v>
+        <v>13138000</v>
       </c>
       <c r="X3" s="5" t="n">
-        <v>12665000</v>
+        <v>12729000</v>
       </c>
       <c r="Y3" s="5" t="n">
-        <v>13903000</v>
+        <v>13970000</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>13179000</v>
+        <v>13242000</v>
       </c>
       <c r="AA3" s="5" t="n">
-        <v>13384000</v>
+        <v>13454000</v>
       </c>
       <c r="AB3" s="5" t="n">
-        <v>12234000</v>
+        <v>12298000</v>
       </c>
       <c r="AC3" s="5" t="n">
-        <v>12246000</v>
+        <v>12309000</v>
       </c>
       <c r="AD3" s="5" t="n">
-        <v>11795000</v>
+        <v>11848000</v>
       </c>
       <c r="AE3" s="5" t="n">
-        <v>11959000</v>
+        <v>12020000</v>
       </c>
       <c r="AF3" s="5" t="n">
-        <v>13405000</v>
+        <v>13470000</v>
       </c>
       <c r="AG3" s="5" t="n">
-        <v>13019000</v>
+        <v>13079000</v>
       </c>
       <c r="AH3" s="5" t="n">
-        <v>13266000</v>
+        <v>13322000</v>
       </c>
       <c r="AI3" s="5" t="n">
-        <v>12049000</v>
+        <v>12103000</v>
       </c>
       <c r="AJ3" s="5" t="n">
-        <v>11857000</v>
+        <v>11920000</v>
       </c>
       <c r="AK3" s="5" t="n">
-        <v>12550000</v>
+        <v>12608000</v>
       </c>
       <c r="AL3" s="5" t="n">
-        <v>12127000</v>
+        <v>12192000</v>
       </c>
       <c r="AM3" s="5" t="n">
-        <v>11775000</v>
+        <v>11856000</v>
       </c>
       <c r="AN3" s="5" t="n">
-        <v>10590000</v>
+        <v>10648000</v>
       </c>
       <c r="AO3" s="5" t="n">
-        <v>10610000</v>
+        <v>10664000</v>
       </c>
       <c r="AP3" s="5" t="n">
         <v>10080000</v>
@@ -37408,17 +37408,17 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>5233814</v>
+        <v>5250519</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>4736423</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>497391</v>
+        <v>514096</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>+10.5%</t>
+          <t>+10.8%</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -46719,14 +46719,14 @@
         <v>14883000</v>
       </c>
       <c r="D294" s="4" t="n">
-        <v>13761000</v>
+        <v>13810000</v>
       </c>
       <c r="E294" s="4" t="n">
-        <v>1122000</v>
+        <v>1073000</v>
       </c>
       <c r="F294" s="4" t="inlineStr">
         <is>
-          <t>+8.2%</t>
+          <t>+7.8%</t>
         </is>
       </c>
       <c r="G294" s="4" t="inlineStr">
@@ -46751,14 +46751,14 @@
         <v>12778000</v>
       </c>
       <c r="D295" s="5" t="n">
-        <v>12263000</v>
+        <v>12305000</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>515000</v>
+        <v>473000</v>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="G295" s="5" t="inlineStr">
@@ -46783,14 +46783,14 @@
         <v>13586000</v>
       </c>
       <c r="D296" s="4" t="n">
-        <v>13292000</v>
+        <v>13352000</v>
       </c>
       <c r="E296" s="4" t="n">
-        <v>294000</v>
+        <v>234000</v>
       </c>
       <c r="F296" s="4" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="G296" s="4" t="inlineStr">
@@ -46815,14 +46815,14 @@
         <v>12533000</v>
       </c>
       <c r="D297" s="5" t="n">
-        <v>12527000</v>
+        <v>12590000</v>
       </c>
       <c r="E297" s="5" t="n">
-        <v>6000</v>
+        <v>-57000</v>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -46847,14 +46847,14 @@
         <v>12894000</v>
       </c>
       <c r="D298" s="4" t="n">
-        <v>12586000</v>
+        <v>12643000</v>
       </c>
       <c r="E298" s="4" t="n">
-        <v>308000</v>
+        <v>251000</v>
       </c>
       <c r="F298" s="4" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+2.0%</t>
         </is>
       </c>
       <c r="G298" s="4" t="inlineStr">
@@ -46879,14 +46879,14 @@
         <v>15048000</v>
       </c>
       <c r="D299" s="5" t="n">
-        <v>14788000</v>
+        <v>14860000</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>260000</v>
+        <v>188000</v>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+1.3%</t>
         </is>
       </c>
       <c r="G299" s="5" t="inlineStr">
@@ -46911,14 +46911,14 @@
         <v>14638000</v>
       </c>
       <c r="D300" s="4" t="n">
-        <v>13957000</v>
+        <v>14027000</v>
       </c>
       <c r="E300" s="4" t="n">
-        <v>681000</v>
+        <v>611000</v>
       </c>
       <c r="F300" s="4" t="inlineStr">
         <is>
-          <t>+4.9%</t>
+          <t>+4.4%</t>
         </is>
       </c>
       <c r="G300" s="4" t="inlineStr">
@@ -46943,14 +46943,14 @@
         <v>14423000</v>
       </c>
       <c r="D301" s="5" t="n">
-        <v>13790000</v>
+        <v>13870000</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>633000</v>
+        <v>553000</v>
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="G301" s="5" t="inlineStr">
@@ -46975,14 +46975,14 @@
         <v>13687000</v>
       </c>
       <c r="D302" s="4" t="n">
-        <v>13085000</v>
+        <v>13138000</v>
       </c>
       <c r="E302" s="4" t="n">
-        <v>602000</v>
+        <v>549000</v>
       </c>
       <c r="F302" s="4" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="G302" s="4" t="inlineStr">
@@ -47007,14 +47007,14 @@
         <v>13175000</v>
       </c>
       <c r="D303" s="5" t="n">
-        <v>12665000</v>
+        <v>12729000</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>510000</v>
+        <v>446000</v>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
-          <t>+4.0%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="G303" s="5" t="inlineStr">
@@ -47036,17 +47036,17 @@
         </is>
       </c>
       <c r="C304" s="4" t="n">
-        <v>14427000</v>
+        <v>14488000</v>
       </c>
       <c r="D304" s="4" t="n">
-        <v>13903000</v>
+        <v>13970000</v>
       </c>
       <c r="E304" s="4" t="n">
-        <v>524000</v>
+        <v>518000</v>
       </c>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="G304" s="4" t="inlineStr">
@@ -47068,17 +47068,17 @@
         </is>
       </c>
       <c r="C305" s="5" t="n">
-        <v>14066000</v>
+        <v>14120000</v>
       </c>
       <c r="D305" s="5" t="n">
-        <v>13179000</v>
+        <v>13242000</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>887000</v>
+        <v>878000</v>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
-          <t>+6.7%</t>
+          <t>+6.6%</t>
         </is>
       </c>
       <c r="G305" s="5" t="inlineStr">
@@ -47100,17 +47100,17 @@
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>13761000</v>
+        <v>13810000</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>13384000</v>
+        <v>13454000</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>377000</v>
+        <v>356000</v>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
@@ -47132,17 +47132,17 @@
         </is>
       </c>
       <c r="C307" s="5" t="n">
-        <v>12263000</v>
+        <v>12305000</v>
       </c>
       <c r="D307" s="5" t="n">
-        <v>12234000</v>
+        <v>12298000</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>29000</v>
+        <v>7000</v>
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="G307" s="5" t="inlineStr">
@@ -47164,13 +47164,13 @@
         </is>
       </c>
       <c r="C308" s="4" t="n">
-        <v>13292000</v>
+        <v>13352000</v>
       </c>
       <c r="D308" s="4" t="n">
-        <v>12246000</v>
+        <v>12309000</v>
       </c>
       <c r="E308" s="4" t="n">
-        <v>1046000</v>
+        <v>1043000</v>
       </c>
       <c r="F308" s="4" t="inlineStr">
         <is>
@@ -47196,17 +47196,17 @@
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>12527000</v>
+        <v>12590000</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>11795000</v>
+        <v>11848000</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>732000</v>
+        <v>742000</v>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>+6.3%</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
@@ -47228,13 +47228,13 @@
         </is>
       </c>
       <c r="C310" s="4" t="n">
-        <v>12586000</v>
+        <v>12643000</v>
       </c>
       <c r="D310" s="4" t="n">
-        <v>11959000</v>
+        <v>12020000</v>
       </c>
       <c r="E310" s="4" t="n">
-        <v>627000</v>
+        <v>623000</v>
       </c>
       <c r="F310" s="4" t="inlineStr">
         <is>
@@ -47260,13 +47260,13 @@
         </is>
       </c>
       <c r="C311" s="5" t="n">
-        <v>14788000</v>
+        <v>14860000</v>
       </c>
       <c r="D311" s="5" t="n">
-        <v>13405000</v>
+        <v>13470000</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>1383000</v>
+        <v>1390000</v>
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
@@ -47292,13 +47292,13 @@
         </is>
       </c>
       <c r="C312" s="4" t="n">
-        <v>13957000</v>
+        <v>14027000</v>
       </c>
       <c r="D312" s="4" t="n">
-        <v>13019000</v>
+        <v>13079000</v>
       </c>
       <c r="E312" s="4" t="n">
-        <v>938000</v>
+        <v>948000</v>
       </c>
       <c r="F312" s="4" t="inlineStr">
         <is>
@@ -47324,17 +47324,17 @@
         </is>
       </c>
       <c r="C313" s="5" t="n">
-        <v>13790000</v>
+        <v>13870000</v>
       </c>
       <c r="D313" s="5" t="n">
-        <v>13266000</v>
+        <v>13322000</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>524000</v>
+        <v>548000</v>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
-          <t>+4.0%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="G313" s="5" t="inlineStr">
@@ -47356,13 +47356,13 @@
         </is>
       </c>
       <c r="C314" s="4" t="n">
-        <v>13085000</v>
+        <v>13138000</v>
       </c>
       <c r="D314" s="4" t="n">
-        <v>12049000</v>
+        <v>12103000</v>
       </c>
       <c r="E314" s="4" t="n">
-        <v>1036000</v>
+        <v>1035000</v>
       </c>
       <c r="F314" s="4" t="inlineStr">
         <is>
@@ -47388,13 +47388,13 @@
         </is>
       </c>
       <c r="C315" s="5" t="n">
-        <v>12665000</v>
+        <v>12729000</v>
       </c>
       <c r="D315" s="5" t="n">
-        <v>11857000</v>
+        <v>11920000</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>808000</v>
+        <v>809000</v>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
@@ -47420,13 +47420,13 @@
         </is>
       </c>
       <c r="C316" s="4" t="n">
-        <v>13903000</v>
+        <v>13970000</v>
       </c>
       <c r="D316" s="4" t="n">
-        <v>12550000</v>
+        <v>12608000</v>
       </c>
       <c r="E316" s="4" t="n">
-        <v>1353000</v>
+        <v>1362000</v>
       </c>
       <c r="F316" s="4" t="inlineStr">
         <is>
@@ -47452,17 +47452,17 @@
         </is>
       </c>
       <c r="C317" s="5" t="n">
-        <v>13179000</v>
+        <v>13242000</v>
       </c>
       <c r="D317" s="5" t="n">
-        <v>12127000</v>
+        <v>12192000</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>1052000</v>
+        <v>1050000</v>
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
-          <t>+8.7%</t>
+          <t>+8.6%</t>
         </is>
       </c>
       <c r="G317" s="5" t="inlineStr">
@@ -47484,17 +47484,17 @@
         </is>
       </c>
       <c r="C318" s="4" t="n">
-        <v>13384000</v>
+        <v>13454000</v>
       </c>
       <c r="D318" s="4" t="n">
-        <v>11775000</v>
+        <v>11856000</v>
       </c>
       <c r="E318" s="4" t="n">
-        <v>1609000</v>
+        <v>1598000</v>
       </c>
       <c r="F318" s="4" t="inlineStr">
         <is>
-          <t>+13.7%</t>
+          <t>+13.5%</t>
         </is>
       </c>
       <c r="G318" s="4" t="inlineStr">
@@ -47516,13 +47516,13 @@
         </is>
       </c>
       <c r="C319" s="5" t="n">
-        <v>12234000</v>
+        <v>12298000</v>
       </c>
       <c r="D319" s="5" t="n">
-        <v>10590000</v>
+        <v>10648000</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>1644000</v>
+        <v>1650000</v>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
@@ -47548,13 +47548,13 @@
         </is>
       </c>
       <c r="C320" s="4" t="n">
-        <v>12246000</v>
+        <v>12309000</v>
       </c>
       <c r="D320" s="4" t="n">
-        <v>10610000</v>
+        <v>10664000</v>
       </c>
       <c r="E320" s="4" t="n">
-        <v>1636000</v>
+        <v>1645000</v>
       </c>
       <c r="F320" s="4" t="inlineStr">
         <is>
@@ -47580,17 +47580,17 @@
         </is>
       </c>
       <c r="C321" s="5" t="n">
-        <v>11795000</v>
+        <v>11848000</v>
       </c>
       <c r="D321" s="5" t="n">
         <v>10080000</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>1715000</v>
+        <v>1768000</v>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>+17.0%</t>
+          <t>+17.5%</t>
         </is>
       </c>
       <c r="G321" s="5" t="inlineStr">
@@ -47612,17 +47612,17 @@
         </is>
       </c>
       <c r="C322" s="4" t="n">
-        <v>11959000</v>
+        <v>12020000</v>
       </c>
       <c r="D322" s="4" t="n">
         <v>10613000</v>
       </c>
       <c r="E322" s="4" t="n">
-        <v>1346000</v>
+        <v>1407000</v>
       </c>
       <c r="F322" s="4" t="inlineStr">
         <is>
-          <t>+12.7%</t>
+          <t>+13.3%</t>
         </is>
       </c>
       <c r="G322" s="4" t="inlineStr">
@@ -47644,17 +47644,17 @@
         </is>
       </c>
       <c r="C323" s="5" t="n">
-        <v>13405000</v>
+        <v>13470000</v>
       </c>
       <c r="D323" s="5" t="n">
         <v>11508000</v>
       </c>
       <c r="E323" s="5" t="n">
-        <v>1897000</v>
+        <v>1962000</v>
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
-          <t>+16.5%</t>
+          <t>+17.1%</t>
         </is>
       </c>
       <c r="G323" s="5" t="inlineStr">
@@ -47676,17 +47676,17 @@
         </is>
       </c>
       <c r="C324" s="4" t="n">
-        <v>13019000</v>
+        <v>13079000</v>
       </c>
       <c r="D324" s="4" t="n">
         <v>11195000</v>
       </c>
       <c r="E324" s="4" t="n">
-        <v>1824000</v>
+        <v>1884000</v>
       </c>
       <c r="F324" s="4" t="inlineStr">
         <is>
-          <t>+16.3%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="G324" s="4" t="inlineStr">
@@ -47708,17 +47708,17 @@
         </is>
       </c>
       <c r="C325" s="5" t="n">
-        <v>13266000</v>
+        <v>13322000</v>
       </c>
       <c r="D325" s="5" t="n">
         <v>10838000</v>
       </c>
       <c r="E325" s="5" t="n">
-        <v>2428000</v>
+        <v>2484000</v>
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
-          <t>+22.4%</t>
+          <t>+22.9%</t>
         </is>
       </c>
       <c r="G325" s="5" t="inlineStr">
@@ -47740,17 +47740,17 @@
         </is>
       </c>
       <c r="C326" s="4" t="n">
-        <v>12049000</v>
+        <v>12103000</v>
       </c>
       <c r="D326" s="4" t="n">
         <v>9609000</v>
       </c>
       <c r="E326" s="4" t="n">
-        <v>2440000</v>
+        <v>2494000</v>
       </c>
       <c r="F326" s="4" t="inlineStr">
         <is>
-          <t>+25.4%</t>
+          <t>+25.9%</t>
         </is>
       </c>
       <c r="G326" s="4" t="inlineStr">
@@ -47772,17 +47772,17 @@
         </is>
       </c>
       <c r="C327" s="5" t="n">
-        <v>11857000</v>
+        <v>11920000</v>
       </c>
       <c r="D327" s="5" t="n">
         <v>9457000</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>2400000</v>
+        <v>2463000</v>
       </c>
       <c r="F327" s="5" t="inlineStr">
         <is>
-          <t>+25.4%</t>
+          <t>+26.0%</t>
         </is>
       </c>
       <c r="G327" s="5" t="inlineStr">
@@ -47804,17 +47804,17 @@
         </is>
       </c>
       <c r="C328" s="6" t="n">
-        <v>12550000</v>
+        <v>12608000</v>
       </c>
       <c r="D328" s="6" t="n">
         <v>9651000</v>
       </c>
       <c r="E328" s="6" t="n">
-        <v>2899000</v>
+        <v>2957000</v>
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>+30.0%</t>
+          <t>+30.6%</t>
         </is>
       </c>
       <c r="G328" s="6" t="inlineStr">
@@ -47836,17 +47836,17 @@
         </is>
       </c>
       <c r="C329" s="6" t="n">
-        <v>12127000</v>
+        <v>12192000</v>
       </c>
       <c r="D329" s="6" t="n">
         <v>9197000</v>
       </c>
       <c r="E329" s="6" t="n">
-        <v>2930000</v>
+        <v>2995000</v>
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>+31.9%</t>
+          <t>+32.6%</t>
         </is>
       </c>
       <c r="G329" s="6" t="inlineStr">
@@ -47868,17 +47868,17 @@
         </is>
       </c>
       <c r="C330" s="6" t="n">
-        <v>11775000</v>
+        <v>11856000</v>
       </c>
       <c r="D330" s="6" t="n">
         <v>9065000</v>
       </c>
       <c r="E330" s="6" t="n">
-        <v>2710000</v>
+        <v>2791000</v>
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>+29.9%</t>
+          <t>+30.8%</t>
         </is>
       </c>
       <c r="G330" s="6" t="inlineStr">
@@ -47900,17 +47900,17 @@
         </is>
       </c>
       <c r="C331" s="6" t="n">
-        <v>10590000</v>
+        <v>10648000</v>
       </c>
       <c r="D331" s="6" t="n">
         <v>7401000</v>
       </c>
       <c r="E331" s="6" t="n">
-        <v>3189000</v>
+        <v>3247000</v>
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>+43.1%</t>
+          <t>+43.9%</t>
         </is>
       </c>
       <c r="G331" s="6" t="inlineStr">
@@ -47932,17 +47932,17 @@
         </is>
       </c>
       <c r="C332" s="4" t="n">
-        <v>10610000</v>
+        <v>10664000</v>
       </c>
       <c r="D332" s="4" t="n">
         <v>7391000</v>
       </c>
       <c r="E332" s="4" t="n">
-        <v>3219000</v>
+        <v>3273000</v>
       </c>
       <c r="F332" s="4" t="inlineStr">
         <is>
-          <t>+43.5%</t>
+          <t>+44.3%</t>
         </is>
       </c>
       <c r="G332" s="4" t="inlineStr">
@@ -59212,7 +59212,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 07, 2026 at 16:00 UTC</t>
+          <t>Last updated: May 12, 2026 at 16:15 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:31Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
         </is>
       </c>
       <c r="F294" s="4" t="n">
-        <v>1629743</v>
+        <v>1815893</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:10Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18543,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19095,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22499,7 +22499,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23005,7 +23005,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23143,7 +23143,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23189,7 +23189,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23695,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24581,7 +24581,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24781,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25081,7 +25081,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25131,7 +25131,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25631,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25831,7 +25831,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25881,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -25981,7 +25981,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26531,7 +26531,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27481,7 +27481,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27631,7 +27631,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27731,7 +27731,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="L585" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="L587" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28177,7 +28177,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="L589" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="L591" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28477,7 +28477,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="L595" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28577,7 +28577,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="L597" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="L599" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="L601" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L603" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="L605" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="L607" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29227,7 +29227,7 @@
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29377,7 +29377,7 @@
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="L615" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="L617" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29727,7 +29727,7 @@
       </c>
       <c r="L619" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29827,7 @@
       </c>
       <c r="L621" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29877,7 +29877,7 @@
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="L625" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="L627" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30227,7 +30227,7 @@
       </c>
       <c r="L629" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30327,7 +30327,7 @@
       </c>
       <c r="L631" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30377,7 +30377,7 @@
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="L633" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30477,7 +30477,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="L635" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="L637" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30677,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="L639" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30777,7 +30777,7 @@
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="L641" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="L644" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31027,7 +31027,7 @@
       </c>
       <c r="L645" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="L646" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="L647" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31177,7 +31177,7 @@
       </c>
       <c r="L648" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="L649" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31327,7 +31327,7 @@
       </c>
       <c r="L651" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31377,7 @@
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="L655" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="L657" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31727,7 +31727,7 @@
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="L661" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="L663" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="L665" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32077,7 +32077,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32127,7 +32127,7 @@
       </c>
       <c r="L667" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32227,7 @@
       </c>
       <c r="L669" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="L671" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32377,7 @@
       </c>
       <c r="L672" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="L673" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="L674" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L675" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="L676" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32677,7 @@
       </c>
       <c r="L678" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32727,7 +32727,7 @@
       </c>
       <c r="L679" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="L680" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="L681" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32877,7 +32877,7 @@
       </c>
       <c r="L682" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32927,7 @@
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="L684" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33027,7 @@
       </c>
       <c r="L685" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="L686" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="L687" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="L688" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -33227,7 +33227,7 @@
       </c>
       <c r="L689" s="5" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="L690" s="4" t="inlineStr">
         <is>
-          <t>2026-05-12T16:15:11Z</t>
+          <t>2026-05-13T16:14:32Z</t>
         </is>
       </c>
     </row>
@@ -59212,7 +59212,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 12, 2026 at 16:15 UTC</t>
+          <t>Last updated: May 13, 2026 at 16:14 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:31Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
         </is>
       </c>
       <c r="F294" s="4" t="n">
-        <v>1815893</v>
+        <v>2255242</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18543,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19095,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22499,7 +22499,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -23005,7 +23005,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:16Z</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23143,7 +23143,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23189,7 +23189,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23695,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24581,7 +24581,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24781,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25081,7 +25081,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25131,7 +25131,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25631,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25831,7 +25831,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25881,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -25981,7 +25981,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26531,7 +26531,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27481,7 +27481,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27631,7 +27631,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27731,7 +27731,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="L585" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="L587" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28177,7 +28177,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="L589" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="L591" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28477,7 +28477,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="L595" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28577,7 +28577,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="L597" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="L599" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="L601" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L603" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="L605" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="L607" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29227,7 +29227,7 @@
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29377,7 +29377,7 @@
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="L615" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="L617" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29727,7 +29727,7 @@
       </c>
       <c r="L619" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29827,7 @@
       </c>
       <c r="L621" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29877,7 +29877,7 @@
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="L625" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="L627" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30227,7 +30227,7 @@
       </c>
       <c r="L629" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30327,7 +30327,7 @@
       </c>
       <c r="L631" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30377,7 +30377,7 @@
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="L633" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30477,7 +30477,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="L635" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="L637" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30677,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="L639" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30777,7 +30777,7 @@
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="L641" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="L644" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31027,7 +31027,7 @@
       </c>
       <c r="L645" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="L646" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="L647" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31177,7 +31177,7 @@
       </c>
       <c r="L648" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="L649" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31327,7 +31327,7 @@
       </c>
       <c r="L651" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31377,7 @@
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="L655" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="L657" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31727,7 +31727,7 @@
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="L661" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="L663" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="L665" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32077,7 +32077,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32127,7 +32127,7 @@
       </c>
       <c r="L667" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32227,7 @@
       </c>
       <c r="L669" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="L671" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32377,7 @@
       </c>
       <c r="L672" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="L673" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="L674" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L675" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="L676" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32677,7 @@
       </c>
       <c r="L678" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32727,7 +32727,7 @@
       </c>
       <c r="L679" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="L680" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="L681" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32877,7 +32877,7 @@
       </c>
       <c r="L682" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32927,7 @@
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="L684" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33027,7 @@
       </c>
       <c r="L685" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="L686" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="L687" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="L688" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -33227,7 +33227,7 @@
       </c>
       <c r="L689" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="L690" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13T16:14:32Z</t>
+          <t>2026-05-14T16:06:17Z</t>
         </is>
       </c>
     </row>
@@ -59212,7 +59212,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 13, 2026 at 16:14 UTC</t>
+          <t>Last updated: May 14, 2026 at 16:06 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:11Z</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8997,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10009,7 +10009,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10929,7 +10929,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11021,7 +11021,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11343,7 +11343,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12033,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12539,7 +12539,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12769,7 +12769,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13459,7 +13459,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13945,7 +13945,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14107,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14269,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
         </is>
       </c>
       <c r="F294" s="4" t="n">
-        <v>2255242</v>
+        <v>2889362</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14403,7 +14403,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14449,7 +14449,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14817,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15047,7 +15047,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15277,7 +15277,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15553,7 +15553,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15737,7 +15737,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16013,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16427,7 +16427,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16519,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16565,7 +16565,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16795,7 +16795,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16979,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17025,7 +17025,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17163,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17623,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17761,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17807,7 +17807,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -17991,7 +17991,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18175,7 +18175,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18221,7 +18221,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18405,7 +18405,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18543,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18589,7 +18589,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18681,7 +18681,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18727,7 +18727,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18911,7 +18911,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19003,7 +19003,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19095,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19279,7 +19279,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19509,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19601,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19739,7 +19739,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19785,7 +19785,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19877,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19923,7 +19923,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19969,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20061,7 +20061,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20475,7 +20475,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20659,7 +20659,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20705,7 +20705,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20889,7 +20889,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -20981,7 +20981,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21027,7 +21027,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21073,7 +21073,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21257,7 +21257,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21303,7 +21303,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21349,7 +21349,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21533,7 +21533,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21625,7 +21625,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21809,7 +21809,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21855,7 +21855,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21901,7 +21901,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22269,7 +22269,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22315,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22361,7 +22361,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22499,7 +22499,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22591,7 +22591,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22637,7 +22637,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22729,7 +22729,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23005,7 +23005,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:16Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23143,7 +23143,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23189,7 +23189,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23281,7 +23281,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23327,7 +23327,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23603,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23649,7 +23649,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23695,7 +23695,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23879,7 +23879,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23925,7 +23925,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24247,7 +24247,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24293,7 +24293,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24481,7 +24481,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24581,7 +24581,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24631,7 +24631,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24781,7 +24781,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24831,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24881,7 +24881,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25081,7 +25081,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25131,7 +25131,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25231,7 +25231,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25331,7 +25331,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25531,7 +25531,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25581,7 +25581,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25631,7 +25631,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25681,7 +25681,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25831,7 +25831,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25881,7 +25881,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25931,7 +25931,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -25981,7 +25981,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26031,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26181,7 +26181,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26281,7 +26281,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26331,7 +26331,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26381,7 +26381,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26481,7 +26481,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26531,7 +26531,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27031,7 +27031,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27131,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27231,7 +27231,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27281,7 +27281,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27431,7 +27431,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27481,7 +27481,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27531,7 +27531,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27631,7 +27631,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27681,7 +27681,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27731,7 +27731,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27931,7 +27931,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28031,7 +28031,7 @@
       </c>
       <c r="L585" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28127,7 +28127,7 @@
       </c>
       <c r="L587" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28177,7 +28177,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="L589" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="L591" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28427,7 +28427,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28477,7 +28477,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28527,7 +28527,7 @@
       </c>
       <c r="L595" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28577,7 +28577,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
       </c>
       <c r="L597" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28677,7 +28677,7 @@
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="L599" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28827,7 +28827,7 @@
       </c>
       <c r="L601" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28877,7 +28877,7 @@
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28927,7 +28927,7 @@
       </c>
       <c r="L603" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29027,7 +29027,7 @@
       </c>
       <c r="L605" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29077,7 +29077,7 @@
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29127,7 @@
       </c>
       <c r="L607" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29177,7 +29177,7 @@
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29227,7 +29227,7 @@
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29277,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29377,7 +29377,7 @@
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="L615" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29627,7 +29627,7 @@
       </c>
       <c r="L617" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29727,7 +29727,7 @@
       </c>
       <c r="L619" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29777,7 +29777,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29827,7 +29827,7 @@
       </c>
       <c r="L621" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29877,7 +29877,7 @@
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29927,7 +29927,7 @@
       </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -29977,7 +29977,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="L625" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="L627" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30227,7 +30227,7 @@
       </c>
       <c r="L629" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30277,7 +30277,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30327,7 +30327,7 @@
       </c>
       <c r="L631" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30377,7 +30377,7 @@
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30427,7 +30427,7 @@
       </c>
       <c r="L633" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30477,7 +30477,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30527,7 +30527,7 @@
       </c>
       <c r="L635" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="L637" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30677,7 +30677,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
       </c>
       <c r="L639" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30777,7 +30777,7 @@
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30827,7 +30827,7 @@
       </c>
       <c r="L641" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="L644" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31027,7 +31027,7 @@
       </c>
       <c r="L645" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="L646" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="L647" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31177,7 +31177,7 @@
       </c>
       <c r="L648" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31227,7 +31227,7 @@
       </c>
       <c r="L649" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31277,7 +31277,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31327,7 +31327,7 @@
       </c>
       <c r="L651" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31377,7 @@
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31427,7 +31427,7 @@
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31477,7 +31477,7 @@
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31527,7 +31527,7 @@
       </c>
       <c r="L655" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="L657" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31727,7 +31727,7 @@
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31827,7 +31827,7 @@
       </c>
       <c r="L661" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:12Z</t>
         </is>
       </c>
     </row>
@@ -31877,7 +31877,7 @@
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="L663" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32027,7 +32027,7 @@
       </c>
       <c r="L665" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32077,7 +32077,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32127,7 +32127,7 @@
       </c>
       <c r="L667" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32177,7 +32177,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32227,7 +32227,7 @@
       </c>
       <c r="L669" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32327,7 +32327,7 @@
       </c>
       <c r="L671" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32377,7 +32377,7 @@
       </c>
       <c r="L672" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32427,7 @@
       </c>
       <c r="L673" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32477,7 +32477,7 @@
       </c>
       <c r="L674" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L675" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32577,7 +32577,7 @@
       </c>
       <c r="L676" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32627,7 +32627,7 @@
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32677,7 +32677,7 @@
       </c>
       <c r="L678" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32727,7 +32727,7 @@
       </c>
       <c r="L679" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="L680" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32827,7 +32827,7 @@
       </c>
       <c r="L681" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32877,7 +32877,7 @@
       </c>
       <c r="L682" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32927,7 +32927,7 @@
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="L684" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -33027,7 +33027,7 @@
       </c>
       <c r="L685" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -33077,7 +33077,7 @@
       </c>
       <c r="L686" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -33127,7 +33127,7 @@
       </c>
       <c r="L687" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="L688" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -33227,7 +33227,7 @@
       </c>
       <c r="L689" s="5" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="L690" s="4" t="inlineStr">
         <is>
-          <t>2026-05-14T16:06:17Z</t>
+          <t>2026-05-18T23:39:13Z</t>
         </is>
       </c>
     </row>
@@ -59212,7 +59212,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 14, 2026 at 16:06 UTC</t>
+          <t>Last updated: May 18, 2026 at 23:39 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11182,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11432,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11532,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14532,7 +14532,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="F294" s="4" t="n">
-        <v>2889362</v>
+        <v>3486586</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -15966,7 +15966,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:11Z</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17070,7 +17070,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17806,7 +17806,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18174,7 +18174,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18220,7 +18220,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18312,7 +18312,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18358,7 +18358,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18818,7 +18818,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19232,7 +19232,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19324,7 +19324,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19600,7 +19600,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19692,7 +19692,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:26Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20014,7 +20014,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20060,7 +20060,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20106,7 +20106,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20520,7 +20520,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="L395" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20704,7 +20704,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20750,7 +20750,7 @@
       </c>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20796,7 +20796,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20842,7 +20842,7 @@
       </c>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20888,7 +20888,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21164,7 +21164,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21394,7 +21394,7 @@
       </c>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21440,7 +21440,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21486,7 +21486,7 @@
       </c>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21532,7 +21532,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21578,7 +21578,7 @@
       </c>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21624,7 +21624,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21670,7 +21670,7 @@
       </c>
       <c r="L419" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21716,7 +21716,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21762,7 +21762,7 @@
       </c>
       <c r="L421" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21808,7 +21808,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="L423" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21900,7 +21900,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21946,7 +21946,7 @@
       </c>
       <c r="L425" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -21992,7 +21992,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22038,7 +22038,7 @@
       </c>
       <c r="L427" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22084,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22130,7 +22130,7 @@
       </c>
       <c r="L429" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22222,7 +22222,7 @@
       </c>
       <c r="L431" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22268,7 +22268,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="L433" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="L435" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22452,7 +22452,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22498,7 +22498,7 @@
       </c>
       <c r="L437" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22590,7 +22590,7 @@
       </c>
       <c r="L439" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22682,7 +22682,7 @@
       </c>
       <c r="L441" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22728,7 +22728,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="L443" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22866,7 +22866,7 @@
       </c>
       <c r="L445" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22912,7 +22912,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -22958,7 +22958,7 @@
       </c>
       <c r="L447" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23004,7 +23004,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23050,7 @@
       </c>
       <c r="L449" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23096,7 +23096,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23142,7 +23142,7 @@
       </c>
       <c r="L451" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23234,7 +23234,7 @@
       </c>
       <c r="L453" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23280,7 +23280,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23326,7 +23326,7 @@
       </c>
       <c r="L455" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23372,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="L457" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23464,7 +23464,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="L459" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23556,7 +23556,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="L461" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23648,7 +23648,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="L463" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23740,7 +23740,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23786,7 +23786,7 @@
       </c>
       <c r="L465" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23832,7 +23832,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="L467" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23924,7 +23924,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -23970,7 +23970,7 @@
       </c>
       <c r="L469" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24016,7 +24016,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24062,7 +24062,7 @@
       </c>
       <c r="L471" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24108,7 +24108,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24154,7 +24154,7 @@
       </c>
       <c r="L473" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24246,7 +24246,7 @@
       </c>
       <c r="L475" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24292,7 +24292,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24338,7 +24338,7 @@
       </c>
       <c r="L477" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24384,7 +24384,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24430,7 +24430,7 @@
       </c>
       <c r="L479" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24476,7 +24476,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24522,7 +24522,7 @@
       </c>
       <c r="L481" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24568,7 +24568,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="L483" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24660,7 +24660,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24706,7 +24706,7 @@
       </c>
       <c r="L485" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24752,7 +24752,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
       </c>
       <c r="L487" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24844,7 +24844,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24890,7 +24890,7 @@
       </c>
       <c r="L489" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24936,7 +24936,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="L491" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25028,7 +25028,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25074,7 +25074,7 @@
       </c>
       <c r="L493" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25166,7 +25166,7 @@
       </c>
       <c r="L495" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25212,7 +25212,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25258,7 +25258,7 @@
       </c>
       <c r="L497" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25304,7 +25304,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25350,7 +25350,7 @@
       </c>
       <c r="L499" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25396,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25442,7 +25442,7 @@
       </c>
       <c r="L501" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25488,7 +25488,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="L503" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25580,7 +25580,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25626,7 +25626,7 @@
       </c>
       <c r="L505" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25672,7 +25672,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="L507" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="L508" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25810,7 +25810,7 @@
       </c>
       <c r="L509" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25856,7 +25856,7 @@
       </c>
       <c r="L510" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25902,7 +25902,7 @@
       </c>
       <c r="L511" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25948,7 +25948,7 @@
       </c>
       <c r="L512" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -25994,7 +25994,7 @@
       </c>
       <c r="L513" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
       </c>
       <c r="L514" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26094,7 +26094,7 @@
       </c>
       <c r="L515" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="L516" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26194,7 +26194,7 @@
       </c>
       <c r="L517" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26244,7 +26244,7 @@
       </c>
       <c r="L518" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="L519" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26344,7 +26344,7 @@
       </c>
       <c r="L520" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26394,7 +26394,7 @@
       </c>
       <c r="L521" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="L522" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="L523" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="L524" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26594,7 +26594,7 @@
       </c>
       <c r="L525" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26644,7 +26644,7 @@
       </c>
       <c r="L526" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="L527" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26744,7 +26744,7 @@
       </c>
       <c r="L528" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26794,7 +26794,7 @@
       </c>
       <c r="L529" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26844,7 +26844,7 @@
       </c>
       <c r="L530" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26894,7 +26894,7 @@
       </c>
       <c r="L531" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26944,7 +26944,7 @@
       </c>
       <c r="L532" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -26994,7 +26994,7 @@
       </c>
       <c r="L533" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27044,7 +27044,7 @@
       </c>
       <c r="L534" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27094,7 +27094,7 @@
       </c>
       <c r="L535" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27144,7 +27144,7 @@
       </c>
       <c r="L536" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="L537" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27244,7 +27244,7 @@
       </c>
       <c r="L538" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27294,7 +27294,7 @@
       </c>
       <c r="L539" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27344,7 +27344,7 @@
       </c>
       <c r="L540" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27394,7 +27394,7 @@
       </c>
       <c r="L541" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27444,7 @@
       </c>
       <c r="L542" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="L543" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27544,7 +27544,7 @@
       </c>
       <c r="L544" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27594,7 +27594,7 @@
       </c>
       <c r="L545" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27644,7 +27644,7 @@
       </c>
       <c r="L546" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27694,7 +27694,7 @@
       </c>
       <c r="L547" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="L548" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27794,7 +27794,7 @@
       </c>
       <c r="L549" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27844,7 +27844,7 @@
       </c>
       <c r="L550" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="L551" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27944,7 +27944,7 @@
       </c>
       <c r="L552" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -27994,7 +27994,7 @@
       </c>
       <c r="L553" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28044,7 +28044,7 @@
       </c>
       <c r="L554" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="L555" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28144,7 +28144,7 @@
       </c>
       <c r="L556" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28194,7 +28194,7 @@
       </c>
       <c r="L557" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28244,7 +28244,7 @@
       </c>
       <c r="L558" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28294,7 +28294,7 @@
       </c>
       <c r="L559" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28344,7 +28344,7 @@
       </c>
       <c r="L560" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="L561" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28444,7 +28444,7 @@
       </c>
       <c r="L562" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28494,7 +28494,7 @@
       </c>
       <c r="L563" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28544,7 +28544,7 @@
       </c>
       <c r="L564" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="L565" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28644,7 +28644,7 @@
       </c>
       <c r="L566" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="L567" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28744,7 +28744,7 @@
       </c>
       <c r="L568" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28794,7 +28794,7 @@
       </c>
       <c r="L569" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28844,7 +28844,7 @@
       </c>
       <c r="L570" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28894,7 +28894,7 @@
       </c>
       <c r="L571" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28944,7 +28944,7 @@
       </c>
       <c r="L572" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -28994,7 +28994,7 @@
       </c>
       <c r="L573" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29044,7 +29044,7 @@
       </c>
       <c r="L574" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29094,7 +29094,7 @@
       </c>
       <c r="L575" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29144,7 +29144,7 @@
       </c>
       <c r="L576" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29194,7 +29194,7 @@
       </c>
       <c r="L577" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29244,7 +29244,7 @@
       </c>
       <c r="L578" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="L579" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29344,7 +29344,7 @@
       </c>
       <c r="L580" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29394,7 +29394,7 @@
       </c>
       <c r="L581" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="L582" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29494,7 +29494,7 @@
       </c>
       <c r="L583" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29544,7 +29544,7 @@
       </c>
       <c r="L584" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="L585" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="L586" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29690,7 +29690,7 @@
       </c>
       <c r="L587" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29740,7 +29740,7 @@
       </c>
       <c r="L588" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29790,7 +29790,7 @@
       </c>
       <c r="L589" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="L590" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29890,7 +29890,7 @@
       </c>
       <c r="L591" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29940,7 +29940,7 @@
       </c>
       <c r="L592" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="L593" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30040,7 +30040,7 @@
       </c>
       <c r="L594" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="L595" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30140,7 +30140,7 @@
       </c>
       <c r="L596" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30190,7 +30190,7 @@
       </c>
       <c r="L597" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30240,7 +30240,7 @@
       </c>
       <c r="L598" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30290,7 +30290,7 @@
       </c>
       <c r="L599" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30340,7 +30340,7 @@
       </c>
       <c r="L600" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30390,7 +30390,7 @@
       </c>
       <c r="L601" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30440,7 +30440,7 @@
       </c>
       <c r="L602" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30490,7 +30490,7 @@
       </c>
       <c r="L603" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30540,7 +30540,7 @@
       </c>
       <c r="L604" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30590,7 +30590,7 @@
       </c>
       <c r="L605" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="L606" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30690,7 +30690,7 @@
       </c>
       <c r="L607" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30740,7 +30740,7 @@
       </c>
       <c r="L608" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="L609" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30840,7 +30840,7 @@
       </c>
       <c r="L610" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30890,7 +30890,7 @@
       </c>
       <c r="L611" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30940,7 +30940,7 @@
       </c>
       <c r="L612" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -30990,7 +30990,7 @@
       </c>
       <c r="L613" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31040,7 @@
       </c>
       <c r="L614" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31090,7 +31090,7 @@
       </c>
       <c r="L615" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31140,7 +31140,7 @@
       </c>
       <c r="L616" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="L617" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31240,7 +31240,7 @@
       </c>
       <c r="L618" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31290,7 +31290,7 @@
       </c>
       <c r="L619" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31340,7 +31340,7 @@
       </c>
       <c r="L620" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31390,7 +31390,7 @@
       </c>
       <c r="L621" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31440,7 +31440,7 @@
       </c>
       <c r="L622" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31490,7 +31490,7 @@
       </c>
       <c r="L623" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31540,7 +31540,7 @@
       </c>
       <c r="L624" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31590,7 +31590,7 @@
       </c>
       <c r="L625" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31640,7 +31640,7 @@
       </c>
       <c r="L626" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31690,7 +31690,7 @@
       </c>
       <c r="L627" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31740,7 +31740,7 @@
       </c>
       <c r="L628" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31790,7 +31790,7 @@
       </c>
       <c r="L629" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31840,7 +31840,7 @@
       </c>
       <c r="L630" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31890,7 +31890,7 @@
       </c>
       <c r="L631" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="L632" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -31990,7 +31990,7 @@
       </c>
       <c r="L633" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32040,7 +32040,7 @@
       </c>
       <c r="L634" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32090,7 +32090,7 @@
       </c>
       <c r="L635" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32140,7 +32140,7 @@
       </c>
       <c r="L636" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32190,7 +32190,7 @@
       </c>
       <c r="L637" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32240,7 +32240,7 @@
       </c>
       <c r="L638" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32290,7 +32290,7 @@
       </c>
       <c r="L639" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32340,7 +32340,7 @@
       </c>
       <c r="L640" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="L641" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32440,7 +32440,7 @@
       </c>
       <c r="L642" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32490,7 +32490,7 @@
       </c>
       <c r="L643" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32540,7 +32540,7 @@
       </c>
       <c r="L644" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32590,7 +32590,7 @@
       </c>
       <c r="L645" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32640,7 +32640,7 @@
       </c>
       <c r="L646" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32690,7 +32690,7 @@
       </c>
       <c r="L647" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32740,7 +32740,7 @@
       </c>
       <c r="L648" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32790,7 +32790,7 @@
       </c>
       <c r="L649" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32840,7 +32840,7 @@
       </c>
       <c r="L650" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32890,7 +32890,7 @@
       </c>
       <c r="L651" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32940,7 +32940,7 @@
       </c>
       <c r="L652" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -32990,7 +32990,7 @@
       </c>
       <c r="L653" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33040,7 +33040,7 @@
       </c>
       <c r="L654" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33090,7 +33090,7 @@
       </c>
       <c r="L655" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33140,7 +33140,7 @@
       </c>
       <c r="L656" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33190,7 +33190,7 @@
       </c>
       <c r="L657" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33240,7 +33240,7 @@
       </c>
       <c r="L658" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33290,7 +33290,7 @@
       </c>
       <c r="L659" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33340,7 +33340,7 @@
       </c>
       <c r="L660" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33390,7 +33390,7 @@
       </c>
       <c r="L661" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="L662" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33490,7 +33490,7 @@
       </c>
       <c r="L663" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33540,7 +33540,7 @@
       </c>
       <c r="L664" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="L665" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33640,7 +33640,7 @@
       </c>
       <c r="L666" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33690,7 +33690,7 @@
       </c>
       <c r="L667" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33740,7 +33740,7 @@
       </c>
       <c r="L668" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33790,7 +33790,7 @@
       </c>
       <c r="L669" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33840,7 +33840,7 @@
       </c>
       <c r="L670" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33890,7 +33890,7 @@
       </c>
       <c r="L671" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33940,7 +33940,7 @@
       </c>
       <c r="L672" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -33990,7 +33990,7 @@
       </c>
       <c r="L673" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34040,7 +34040,7 @@
       </c>
       <c r="L674" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34090,7 +34090,7 @@
       </c>
       <c r="L675" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34140,7 +34140,7 @@
       </c>
       <c r="L676" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34190,7 +34190,7 @@
       </c>
       <c r="L677" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34240,7 +34240,7 @@
       </c>
       <c r="L678" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34290,7 +34290,7 @@
       </c>
       <c r="L679" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="L680" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34390,7 +34390,7 @@
       </c>
       <c r="L681" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="L682" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34490,7 +34490,7 @@
       </c>
       <c r="L683" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34540,7 +34540,7 @@
       </c>
       <c r="L684" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34590,7 +34590,7 @@
       </c>
       <c r="L685" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34640,7 +34640,7 @@
       </c>
       <c r="L686" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34690,7 +34690,7 @@
       </c>
       <c r="L687" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34740,7 +34740,7 @@
       </c>
       <c r="L688" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="L689" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34840,7 +34840,7 @@
       </c>
       <c r="L690" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -34884,7 +34884,7 @@
       </c>
       <c r="L691" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21T16:35:27Z</t>
+          <t>2026-05-22T16:16:12Z</t>
         </is>
       </c>
     </row>
@@ -60793,7 +60793,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Last updated: May 21, 2026 at 16:35 UTC</t>
+          <t>Last updated: May 22, 2026 at 16:16 UTC</t>
         </is>
       </c>
     </row>

--- a/data/public/bcn_transit_master.xlsx
+++ b/data/public/bcn_transit_master.xlsx
@@ -2100,7 +2100,7 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="L135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="L147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="L149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11182,7 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11432,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11532,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11732,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11832,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12782,7 +12782,7 @@
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="L241" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="L243" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="L245" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13582,7 +13582,7 @@
       </c>
       <c r="L247" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="L249" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="L251" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="L253" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="L255" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="L257" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="L259" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="L263" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14432,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14482,7 @@
       </c>
       <c r="L265" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14532,7 +14532,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="L267" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14632,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="L269" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="L271" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14882,7 +14882,7 @@
       </c>
       <c r="L273" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="L275" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="L277" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="L279" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="L281" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15382,7 +15382,7 @@
       </c>
       <c r="L283" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="L285" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="L287" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="L289" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="L291" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15832,7 +15832,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
       </c>
       <c r="L293" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
         </is>
       </c>
       <c r="F294" s="4" t="n">
-        <v>3486586</v>
+        <v>3704773</v>
       </c>
       <c r="G294" s="4" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -15966,7 +15966,7 @@
       </c>
       <c r="L295" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="L297" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16104,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="L299" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:11Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="L301" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="L303" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="L305" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16472,7 +16472,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="L307" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="L309" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16702,7 +16702,7 @@
       </c>
       <c r="L311" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16748,7 +16748,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16794,7 @@
       </c>
       <c r="L313" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="L317" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17024,7 +17024,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17070,7 +17070,7 @@
       </c>
       <c r="L319" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="L321" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17346,7 @@
       </c>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17438,7 +17438,7 @@
       </c>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17530,7 +17530,7 @@
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17622,7 +17622,7 @@
       </c>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17806,7 +17806,7 @@
       </c>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18174,7 +18174,7 @@
       </c>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18220,7 +18220,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18312,7 +18312,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18358,7 +18358,7 @@
       </c>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18450,7 +18450,7 @@
       </c>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18772,7 +18772,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18818,7 +18818,7 @@
       </c>
       <c r="L357" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18864,7 +18864,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="L359" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -18956,7 +18956,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="L361" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19048,7 +19048,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="L363" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="L365" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19232,7 +19232,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="L367" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19324,7 +19324,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19370,7 @@
       </c>
       <c r="L369" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="L371" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="L373" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19600,7 +19600,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="L375" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19692,7 +19692,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="L377" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19830,7 +19830,7 @@
       </c>
       <c r="L379" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="L381" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20014,7 +20014,7 @@
       </c>
       <c r="L383" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20060,7 +20060,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20106,7 +20106,7 @@
       </c>
       <c r="L385" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20152,7 +20152,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="L387" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="L389" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="L391" s="5" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20428,7 +20428,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>2026-05-22T16:16:12Z</t>
+          <t>2026-05-25T16:16:45Z</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="L393" s="5" t="inlineStr">
         <is>
